--- a/JapaneseFlashcards/input/vocabulary.xlsx
+++ b/JapaneseFlashcards/input/vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\buidu\OneDrive\Máy tính\pythontool\JapaneseFlashcards\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13DB63FF-6B85-4987-A5A6-6D206DA6CEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7382ADB3-6DC0-4EDB-B412-5D627EAE44D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1140" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="979">
   <si>
     <t>Japanese</t>
   </si>
@@ -33,61 +33,2935 @@
     <t>Reading</t>
   </si>
   <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>ExampleMeaning</t>
+  </si>
+  <si>
+    <t>海</t>
+  </si>
+  <si>
+    <t>うみ</t>
+  </si>
+  <si>
+    <t>Biển</t>
+  </si>
+  <si>
+    <t>川</t>
+  </si>
+  <si>
+    <t>かわ</t>
+  </si>
+  <si>
+    <t>Sông</t>
+  </si>
+  <si>
+    <t>空</t>
+  </si>
+  <si>
+    <t>そら</t>
+  </si>
+  <si>
+    <t>Bầu trời</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>やま</t>
+  </si>
+  <si>
+    <t>私</t>
+  </si>
+  <si>
+    <t>わたし</t>
+  </si>
+  <si>
+    <t>夏に海へ行きます。</t>
+  </si>
+  <si>
+    <t>Mùa hè tôi đi biển.</t>
+  </si>
+  <si>
+    <t>川で魚を釣ります。</t>
+  </si>
+  <si>
+    <t>Câu cá ở sông.</t>
+  </si>
+  <si>
+    <t>今日は空がきれいです。</t>
+  </si>
+  <si>
+    <t>Hôm nay bầu trời rất đẹp.</t>
+  </si>
+  <si>
+    <t>Núi</t>
+  </si>
+  <si>
+    <t>富士山は高い山です。</t>
+  </si>
+  <si>
+    <t>Núi Phú Sĩ là núi cao.</t>
+  </si>
+  <si>
+    <t>Tôi</t>
+  </si>
+  <si>
+    <t>私は学生です。</t>
+  </si>
+  <si>
+    <t>Tôi là học sinh.</t>
+  </si>
+  <si>
+    <t>人</t>
+  </si>
+  <si>
+    <t>ひと</t>
+  </si>
+  <si>
+    <t>Người</t>
+  </si>
+  <si>
+    <t>あの人は誰ですか。</t>
+  </si>
+  <si>
+    <t>Người kia là ai?</t>
+  </si>
+  <si>
+    <t>友だち</t>
+  </si>
+  <si>
+    <t>ともだち</t>
+  </si>
+  <si>
+    <t>Bạn bè</t>
+  </si>
+  <si>
+    <t>友だちと遊ぶ。</t>
+  </si>
+  <si>
+    <t>Chơi cùng bạn bè.</t>
+  </si>
+  <si>
+    <t>先生</t>
+  </si>
+  <si>
+    <t>せんせい</t>
+  </si>
+  <si>
+    <t>Giáo viên</t>
+  </si>
+  <si>
+    <t>先生に質問します。</t>
+  </si>
+  <si>
+    <t>Hỏi thầy/cô giáo.</t>
+  </si>
+  <si>
+    <t>学生</t>
+  </si>
+  <si>
+    <t>がくせい</t>
+  </si>
+  <si>
+    <t>Học sinh</t>
+  </si>
+  <si>
+    <t>私は日本語の学生です。</t>
+  </si>
+  <si>
+    <t>Tôi là học sinh tiếng Nhật.</t>
+  </si>
+  <si>
+    <t>家族</t>
+  </si>
+  <si>
+    <t>かぞく</t>
+  </si>
+  <si>
+    <t>Gia đình</t>
+  </si>
+  <si>
+    <t>家族は４人です。</t>
+  </si>
+  <si>
+    <t>Gia đình có 4 người.</t>
+  </si>
+  <si>
+    <t>父</t>
+  </si>
+  <si>
+    <t>ちち</t>
+  </si>
+  <si>
+    <t>Bố</t>
+  </si>
+  <si>
+    <t>父は会社員です。</t>
+  </si>
+  <si>
+    <t>Bố tôi là nhân viên công ty.</t>
+  </si>
+  <si>
+    <t>母</t>
+  </si>
+  <si>
+    <t>はは</t>
+  </si>
+  <si>
+    <t>Mẹ</t>
+  </si>
+  <si>
+    <t>母は料理が得意です。</t>
+  </si>
+  <si>
+    <t>Mẹ tôi nấu ăn giỏi.</t>
+  </si>
+  <si>
+    <t>学校</t>
+  </si>
+  <si>
+    <t>がっこう</t>
+  </si>
+  <si>
+    <t>Trường học</t>
+  </si>
+  <si>
+    <t>8時に学校へ行きます。</t>
+  </si>
+  <si>
+    <t>Tôi đến trường lúc 8 giờ.</t>
+  </si>
+  <si>
+    <t>会社</t>
+  </si>
+  <si>
+    <t>かいしゃ</t>
+  </si>
+  <si>
+    <t>Công ty</t>
+  </si>
+  <si>
+    <t>毎日会社で働きます。</t>
+  </si>
+  <si>
+    <t>Hàng ngày tôi làm việc ở công ty.</t>
+  </si>
+  <si>
+    <t>病院</t>
+  </si>
+  <si>
+    <t>びょういん</t>
+  </si>
+  <si>
+    <t>Bệnh viện</t>
+  </si>
+  <si>
+    <t>病院へ行きます。</t>
+  </si>
+  <si>
+    <t>Đi đến bệnh viện.</t>
+  </si>
+  <si>
+    <t>家</t>
+  </si>
+  <si>
+    <t>うち</t>
+  </si>
+  <si>
+    <t>Nhà</t>
+  </si>
+  <si>
+    <t>家へ帰ります。</t>
+  </si>
+  <si>
+    <t>Trở về nhà.</t>
+  </si>
+  <si>
+    <t>部屋</t>
+  </si>
+  <si>
+    <t>へや</t>
+  </si>
+  <si>
+    <t>Phòng</t>
+  </si>
+  <si>
+    <t>部屋を掃除します。</t>
+  </si>
+  <si>
+    <t>Dọn dẹp phòng.</t>
+  </si>
+  <si>
+    <t>本</t>
+  </si>
+  <si>
+    <t>ほん</t>
+  </si>
+  <si>
+    <t>Sách</t>
+  </si>
+  <si>
+    <t>本を読みます。</t>
+  </si>
+  <si>
+    <t>Đọc sách.</t>
+  </si>
+  <si>
+    <t>辞書</t>
+  </si>
+  <si>
+    <t>じしょ</t>
+  </si>
+  <si>
+    <t>Từ điển</t>
+  </si>
+  <si>
+    <t>辞書で言葉を調べます。</t>
+  </si>
+  <si>
+    <t>Tra từ bằng từ điển.</t>
+  </si>
+  <si>
+    <t>車</t>
+  </si>
+  <si>
+    <t>くるま</t>
+  </si>
+  <si>
+    <t>Xe hơi</t>
+  </si>
+  <si>
+    <t>車を運転します。</t>
+  </si>
+  <si>
+    <t>Lái xe hơi.</t>
+  </si>
+  <si>
+    <t>電車</t>
+  </si>
+  <si>
+    <t>でんしゃ</t>
+  </si>
+  <si>
+    <t>Tàu điện</t>
+  </si>
+  <si>
+    <t>電車に乗ります。</t>
+  </si>
+  <si>
+    <t>Đi tàu điện.</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>みず</t>
+  </si>
+  <si>
+    <t>Nước</t>
+  </si>
+  <si>
+    <t>水を飲みます。</t>
+  </si>
+  <si>
+    <t>Uống nước.</t>
+  </si>
+  <si>
+    <t>ご飯</t>
+  </si>
+  <si>
+    <t>ごはん</t>
+  </si>
+  <si>
+    <t>Cơm / Bữa ăn</t>
+  </si>
+  <si>
+    <t>朝ご飯を食べます。</t>
+  </si>
+  <si>
+    <t>Ăn sáng.</t>
+  </si>
+  <si>
+    <t>魚</t>
+  </si>
+  <si>
+    <t>さかな</t>
+  </si>
+  <si>
+    <t>Cá</t>
+  </si>
+  <si>
+    <t>魚が好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích ăn cá.</t>
+  </si>
+  <si>
+    <t>肉</t>
+  </si>
+  <si>
+    <t>にく</t>
+  </si>
+  <si>
+    <t>Thịt</t>
+  </si>
+  <si>
+    <t>牛肉を買いました。</t>
+  </si>
+  <si>
+    <t>Tôi đã mua thịt bò.</t>
+  </si>
+  <si>
+    <t>行く</t>
+  </si>
+  <si>
+    <t>いく</t>
+  </si>
+  <si>
+    <t>Đi</t>
+  </si>
+  <si>
+    <t>スーパーへ行く。</t>
+  </si>
+  <si>
+    <t>Đi siêu thị.</t>
+  </si>
+  <si>
+    <t>来る</t>
+  </si>
+  <si>
+    <t>くる</t>
+  </si>
+  <si>
+    <t>Đến</t>
+  </si>
+  <si>
+    <t>友達が家に来ます。</t>
+  </si>
+  <si>
+    <t>Bạn đến nhà tôi.</t>
+  </si>
+  <si>
+    <t>帰る</t>
+  </si>
+  <si>
+    <t>かえる</t>
+  </si>
+  <si>
+    <t>Về</t>
+  </si>
+  <si>
+    <t>家へ帰る。</t>
+  </si>
+  <si>
+    <t>Về nhà.</t>
+  </si>
+  <si>
+    <t>食べる</t>
+  </si>
+  <si>
+    <t>たべる</t>
+  </si>
+  <si>
+    <t>Ăn</t>
+  </si>
+  <si>
+    <t>パンを食べます。</t>
+  </si>
+  <si>
+    <t>Ăn bánh mì.</t>
+  </si>
+  <si>
+    <t>飲む</t>
+  </si>
+  <si>
+    <t>のむ</t>
+  </si>
+  <si>
+    <t>Uống</t>
+  </si>
+  <si>
+    <t>お茶を飲みます。</t>
+  </si>
+  <si>
+    <t>Uống trà.</t>
+  </si>
+  <si>
+    <t>見る</t>
+  </si>
+  <si>
+    <t>みる</t>
+  </si>
+  <si>
+    <t>Xem / Nhìn</t>
+  </si>
+  <si>
+    <t>映画を見ます。</t>
+  </si>
+  <si>
+    <t>Xem phim.</t>
+  </si>
+  <si>
+    <t>聞く</t>
+  </si>
+  <si>
+    <t>きく</t>
+  </si>
+  <si>
+    <t>Nghe / Hỏi</t>
+  </si>
+  <si>
+    <t>音楽を聞きます。</t>
+  </si>
+  <si>
+    <t>Nghe nhạc.</t>
+  </si>
+  <si>
+    <t>読む</t>
+  </si>
+  <si>
+    <t>よむ</t>
+  </si>
+  <si>
+    <t>Đọc</t>
+  </si>
+  <si>
+    <t>新聞を読みます。</t>
+  </si>
+  <si>
+    <t>Đọc báo.</t>
+  </si>
+  <si>
+    <t>書く</t>
+  </si>
+  <si>
+    <t>かく</t>
+  </si>
+  <si>
+    <t>Viết</t>
+  </si>
+  <si>
+    <t>手紙を書きます。</t>
+  </si>
+  <si>
+    <t>Viết thư.</t>
+  </si>
+  <si>
+    <t>買う</t>
+  </si>
+  <si>
+    <t>かう</t>
+  </si>
+  <si>
+    <t>Mua</t>
+  </si>
+  <si>
+    <t>服を買います。</t>
+  </si>
+  <si>
+    <t>Mua quần áo.</t>
+  </si>
+  <si>
+    <t>会う</t>
+  </si>
+  <si>
+    <t>あう</t>
+  </si>
+  <si>
+    <t>Gặp</t>
+  </si>
+  <si>
+    <t>友達に会います。</t>
+  </si>
+  <si>
+    <t>Gặp bạn bè.</t>
+  </si>
+  <si>
+    <t>大きい</t>
+  </si>
+  <si>
+    <t>おおきい</t>
+  </si>
+  <si>
+    <t>To / Lớn</t>
+  </si>
+  <si>
+    <t>大きい家です。</t>
+  </si>
+  <si>
+    <t>Căn nhà lớn.</t>
+  </si>
+  <si>
+    <t>小さい</t>
+  </si>
+  <si>
+    <t>ちいさい</t>
+  </si>
+  <si>
+    <t>Nhỏ / Bé</t>
+  </si>
+  <si>
+    <t>小さい猫がいます。</t>
+  </si>
+  <si>
+    <t>Có một chú mèo nhỏ.</t>
+  </si>
+  <si>
+    <t>高い</t>
+  </si>
+  <si>
+    <t>たかい</t>
+  </si>
+  <si>
+    <t>Cao / Đắt</t>
+  </si>
+  <si>
+    <t>この本は高いです。</t>
+  </si>
+  <si>
+    <t>Quyển sách này đắt.</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>やすい</t>
+  </si>
+  <si>
+    <t>Rẻ</t>
+  </si>
+  <si>
+    <t>安い服を買いました。</t>
+  </si>
+  <si>
+    <t>Tôi đã mua quần áo rẻ.</t>
+  </si>
+  <si>
+    <t>新しい</t>
+  </si>
+  <si>
+    <t>あたらしい</t>
+  </si>
+  <si>
+    <t>Mới</t>
+  </si>
+  <si>
+    <t>新しい車です。</t>
+  </si>
+  <si>
+    <t>Xe hơi mới.</t>
+  </si>
+  <si>
+    <t>古い</t>
+  </si>
+  <si>
+    <t>ふるい</t>
+  </si>
+  <si>
+    <t>Cũ</t>
+  </si>
+  <si>
+    <t>古い本を読む。</t>
+  </si>
+  <si>
+    <t>Đọc sách cũ.</t>
+  </si>
+  <si>
+    <t>良い</t>
+  </si>
+  <si>
+    <t>いい</t>
+  </si>
+  <si>
+    <t>Tốt</t>
+  </si>
+  <si>
+    <t>天気がいいです。</t>
+  </si>
+  <si>
+    <t>Thời tiết tốt.</t>
+  </si>
+  <si>
+    <t>悪い</t>
+  </si>
+  <si>
+    <t>わるい</t>
+  </si>
+  <si>
+    <t>Xấu / Dở</t>
+  </si>
+  <si>
+    <t>気分が悪い。</t>
+  </si>
+  <si>
+    <t>Cảm thấy không khỏe.</t>
+  </si>
+  <si>
+    <t>楽しい</t>
+  </si>
+  <si>
+    <t>たのしい</t>
+  </si>
+  <si>
+    <t>Vui</t>
+  </si>
+  <si>
+    <t>旅行は楽しかったです。</t>
+  </si>
+  <si>
+    <t>Chuyến du旅行 rất vui.</t>
+  </si>
+  <si>
+    <t>面白い</t>
+  </si>
+  <si>
+    <t>おもしろい</t>
+  </si>
+  <si>
+    <t>Thú vị</t>
+  </si>
+  <si>
+    <t>面白い映画です。</t>
+  </si>
+  <si>
+    <t>Bộ phim thú vị.</t>
+  </si>
+  <si>
+    <t>好き</t>
+  </si>
+  <si>
+    <t>すき</t>
+  </si>
+  <si>
+    <t>Thích</t>
+  </si>
+  <si>
+    <t>日本料理が好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích món ăn Nhật Bản.</t>
+  </si>
+  <si>
+    <t>上手</t>
+  </si>
+  <si>
+    <t>じょうず</t>
+  </si>
+  <si>
+    <t>Giỏi</t>
+  </si>
+  <si>
+    <t>歌が上手です。</t>
+  </si>
+  <si>
+    <t>Hát giỏi.</t>
+  </si>
+  <si>
+    <t>朝</t>
+  </si>
+  <si>
+    <t>あさ</t>
+  </si>
+  <si>
+    <t>Buổi sáng</t>
+  </si>
+  <si>
+    <t>朝6時に起きます。</t>
+  </si>
+  <si>
+    <t>Tôi dậy lúc 6 giờ sáng.</t>
+  </si>
+  <si>
+    <t>昼</t>
+  </si>
+  <si>
+    <t>ひる</t>
+  </si>
+  <si>
+    <t>Buổi trưa</t>
+  </si>
+  <si>
+    <t>昼ご飯を食べます。</t>
+  </si>
+  <si>
+    <t>Tôi ăn cơm trưa.</t>
+  </si>
+  <si>
+    <t>夜</t>
+  </si>
+  <si>
+    <t>よる</t>
+  </si>
+  <si>
+    <t>Buổi tối</t>
+  </si>
+  <si>
+    <t>夜勉強します。</t>
+  </si>
+  <si>
+    <t>Tôi học bài vào buổi tối.</t>
+  </si>
+  <si>
+    <t>今日</t>
+  </si>
+  <si>
+    <t>きょう</t>
+  </si>
+  <si>
+    <t>Hôm nay</t>
+  </si>
+  <si>
+    <t>今日はいい天気です。</t>
+  </si>
+  <si>
+    <t>Hôm nay thời tiết đẹp.</t>
+  </si>
+  <si>
+    <t>明日</t>
+  </si>
+  <si>
+    <t>あした</t>
+  </si>
+  <si>
+    <t>Ngày mai</t>
+  </si>
+  <si>
+    <t>明日買い物に行きます。</t>
+  </si>
+  <si>
+    <t>Ngày mai tôi đi mua sắm.</t>
+  </si>
+  <si>
+    <t>昨日</t>
+  </si>
+  <si>
+    <t>きのう</t>
+  </si>
+  <si>
+    <t>Hôm qua</t>
+  </si>
+  <si>
+    <t>昨日映画を見ました。</t>
+  </si>
+  <si>
+    <t>Hôm qua tôi đã xem phim.</t>
+  </si>
+  <si>
+    <t>毎日</t>
+  </si>
+  <si>
+    <t>まいにち</t>
+  </si>
+  <si>
+    <t>Hàng ngày</t>
+  </si>
+  <si>
+    <t>毎日日本語を勉強します。</t>
+  </si>
+  <si>
+    <t>Hàng ngày tôi học tiếng Nhật.</t>
+  </si>
+  <si>
+    <t>今</t>
+  </si>
+  <si>
+    <t>いま</t>
+  </si>
+  <si>
+    <t>Bây giờ</t>
+  </si>
+  <si>
+    <t>今何時ですか。</t>
+  </si>
+  <si>
+    <t>Bây giờ là mấy giờ?</t>
+  </si>
+  <si>
+    <t>時間</t>
+  </si>
+  <si>
+    <t>じかん</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>時間がありません。</t>
+  </si>
+  <si>
+    <t>Không có thời gian.</t>
+  </si>
+  <si>
+    <t>週</t>
+  </si>
+  <si>
+    <t>しゅう</t>
+  </si>
+  <si>
+    <t>Tuần</t>
+  </si>
+  <si>
+    <t>先週旅行しました。</t>
+  </si>
+  <si>
+    <t>Tuần trước tôi đã đi du lịch.</t>
+  </si>
+  <si>
+    <t>来月</t>
+  </si>
+  <si>
+    <t>らいげつ</t>
+  </si>
+  <si>
+    <t>Tháng sau</t>
+  </si>
+  <si>
+    <t>来月日本へ行きます。</t>
+  </si>
+  <si>
+    <t>Tháng sau tôi sẽ đi Nhật.</t>
+  </si>
+  <si>
+    <t>今年</t>
+  </si>
+  <si>
+    <t>ことし</t>
+  </si>
+  <si>
+    <t>Năm nay</t>
+  </si>
+  <si>
+    <t>今年20歳になります。</t>
+  </si>
+  <si>
+    <t>Năm nay tôi tròn 20 tuổi.</t>
+  </si>
+  <si>
+    <t>話す</t>
+  </si>
+  <si>
+    <t>はなす</t>
+  </si>
+  <si>
+    <t>Nói chuyện</t>
+  </si>
+  <si>
+    <t>日本語で話します。</t>
+  </si>
+  <si>
+    <t>Nói chuyện bằng tiếng Nhật.</t>
+  </si>
+  <si>
+    <t>起きる</t>
+  </si>
+  <si>
+    <t>おきる</t>
+  </si>
+  <si>
+    <t>Thức dậy</t>
+  </si>
+  <si>
+    <t>Thức dậy lúc 6 giờ sáng.</t>
+  </si>
+  <si>
+    <t>寝る</t>
+  </si>
+  <si>
+    <t>ねる</t>
+  </si>
+  <si>
+    <t>Đi ngủ</t>
+  </si>
+  <si>
+    <t>10時に寝ます。</t>
+  </si>
+  <si>
+    <t>Đi ngủ lúc 10 giờ.</t>
+  </si>
+  <si>
+    <t>立つ</t>
+  </si>
+  <si>
+    <t>たつ</t>
+  </si>
+  <si>
+    <t>Đứng</t>
+  </si>
+  <si>
+    <t>ここに立ってください。</t>
+  </si>
+  <si>
+    <t>Hãy đứng ở đây.</t>
+  </si>
+  <si>
+    <t>座る</t>
+  </si>
+  <si>
+    <t>すわる</t>
+  </si>
+  <si>
+    <t>Ngồi</t>
+  </si>
+  <si>
+    <t>椅子に座ります。</t>
+  </si>
+  <si>
+    <t>Ngồi xuống ghế.</t>
+  </si>
+  <si>
+    <t>作る</t>
+  </si>
+  <si>
+    <t>つくる</t>
+  </si>
+  <si>
+    <t>Làm / Chế tạo</t>
+  </si>
+  <si>
+    <t>料理を作ります。</t>
+  </si>
+  <si>
+    <t>Nấu ăn.</t>
+  </si>
+  <si>
+    <t>使う</t>
+  </si>
+  <si>
+    <t>つかう</t>
+  </si>
+  <si>
+    <t>Sử dụng</t>
+  </si>
+  <si>
+    <t>パソコンを使います。</t>
+  </si>
+  <si>
+    <t>Sử dụng máy tính.</t>
+  </si>
+  <si>
+    <t>洗う</t>
+  </si>
+  <si>
+    <t>あらう</t>
+  </si>
+  <si>
+    <t>Rửa</t>
+  </si>
+  <si>
+    <t>手を洗います。</t>
+  </si>
+  <si>
+    <t>Rửa tay.</t>
+  </si>
+  <si>
+    <t>待つ</t>
+  </si>
+  <si>
+    <t>まつ</t>
+  </si>
+  <si>
+    <t>Chờ / Đợi</t>
+  </si>
+  <si>
+    <t>バスを待ちます。</t>
+  </si>
+  <si>
+    <t>Chờ xe buýt.</t>
+  </si>
+  <si>
+    <t>持つ</t>
+  </si>
+  <si>
+    <t>もつ</t>
+  </si>
+  <si>
+    <t>Cầm / Có</t>
+  </si>
+  <si>
+    <t>鞄を持っています。</t>
+  </si>
+  <si>
+    <t>Đang cầm cái cặp.</t>
+  </si>
+  <si>
+    <t>泳ぐ</t>
+  </si>
+  <si>
+    <t>およぐ</t>
+  </si>
+  <si>
+    <t>Bơi</t>
+  </si>
+  <si>
+    <t>プールで泳ぎます。</t>
+  </si>
+  <si>
+    <t>Bơi ở hồ bơi.</t>
+  </si>
+  <si>
+    <t>走る</t>
+  </si>
+  <si>
+    <t>はしる</t>
+  </si>
+  <si>
+    <t>Chạy</t>
+  </si>
+  <si>
+    <t>公園を走ります。</t>
+  </si>
+  <si>
+    <t>Chạy bộ ở công viên.</t>
+  </si>
+  <si>
+    <t>教える</t>
+  </si>
+  <si>
+    <t>おしえる</t>
+  </si>
+  <si>
+    <t>Dạy / Cho biết</t>
+  </si>
+  <si>
+    <t>英語を教えます。</t>
+  </si>
+  <si>
+    <t>Dạy tiếng Anh.</t>
+  </si>
+  <si>
+    <t>習う</t>
+  </si>
+  <si>
+    <t>ならう</t>
+  </si>
+  <si>
+    <t>Học</t>
+  </si>
+  <si>
+    <t>ピアノを習います。</t>
+  </si>
+  <si>
+    <t>Học đàn piano.</t>
+  </si>
+  <si>
+    <t>貸す</t>
+  </si>
+  <si>
+    <t>かす</t>
+  </si>
+  <si>
+    <t>Cho mượn</t>
+  </si>
+  <si>
+    <t>本を貸します。</t>
+  </si>
+  <si>
+    <t>Cho mượn sách.</t>
+  </si>
+  <si>
+    <t>借りる</t>
+  </si>
+  <si>
+    <t>かりる</t>
+  </si>
+  <si>
+    <t>Mượn</t>
+  </si>
+  <si>
+    <t>お金を借ります。</t>
+  </si>
+  <si>
+    <t>Mượn tiền.</t>
+  </si>
+  <si>
+    <t>送る</t>
+  </si>
+  <si>
+    <t>おくる</t>
+  </si>
+  <si>
+    <t>Gửi</t>
+  </si>
+  <si>
+    <t>メールを送ります。</t>
+  </si>
+  <si>
+    <t>Gửi email.</t>
+  </si>
+  <si>
+    <t>切る</t>
+  </si>
+  <si>
+    <t>きる</t>
+  </si>
+  <si>
+    <t>Cắt</t>
+  </si>
+  <si>
+    <t>ハサミで紙を切ります。</t>
+  </si>
+  <si>
+    <t>Cắt giấy bằng kéo.</t>
+  </si>
+  <si>
+    <t>開ける</t>
+  </si>
+  <si>
+    <t>あける</t>
+  </si>
+  <si>
+    <t>Mở</t>
+  </si>
+  <si>
+    <t>ドアを開けます。</t>
+  </si>
+  <si>
+    <t>Mở cửa.</t>
+  </si>
+  <si>
+    <t>閉める</t>
+  </si>
+  <si>
+    <t>しめる</t>
+  </si>
+  <si>
+    <t>Đóng</t>
+  </si>
+  <si>
+    <t>窓を閉めます。</t>
+  </si>
+  <si>
+    <t>Đóng cửa sổ.</t>
+  </si>
+  <si>
+    <t>つける</t>
+  </si>
+  <si>
+    <t>Bật</t>
+  </si>
+  <si>
+    <t>電気をつける。</t>
+  </si>
+  <si>
+    <t>Bật đèn.</t>
+  </si>
+  <si>
+    <t>消す</t>
+  </si>
+  <si>
+    <t>けす</t>
+  </si>
+  <si>
+    <t>Tắt / Xóa</t>
+  </si>
+  <si>
+    <t>テレビを消します。</t>
+  </si>
+  <si>
+    <t>Tắt tivi.</t>
+  </si>
+  <si>
+    <t>入れる</t>
+  </si>
+  <si>
+    <t>いれる</t>
+  </si>
+  <si>
+    <t>Cho vào / Pha</t>
+  </si>
+  <si>
+    <t>コーヒーを入れます。</t>
+  </si>
+  <si>
+    <t>Pha cà phê.</t>
+  </si>
+  <si>
+    <t>出す</t>
+  </si>
+  <si>
+    <t>だす</t>
+  </si>
+  <si>
+    <t>Nộp / Lấy ra</t>
+  </si>
+  <si>
+    <t>宿題を出します。</t>
+  </si>
+  <si>
+    <t>Nộp bài tập về nhà.</t>
+  </si>
+  <si>
+    <t>早い</t>
+  </si>
+  <si>
+    <t>はやい</t>
+  </si>
+  <si>
+    <t>Sớm / Nhanh</t>
+  </si>
+  <si>
+    <t>朝早く起きます。</t>
+  </si>
+  <si>
+    <t>Dậy sớm vào buổi sáng.</t>
+  </si>
+  <si>
+    <t>遅い</t>
+  </si>
+  <si>
+    <t>おそい</t>
+  </si>
+  <si>
+    <t>Chậm / Muộn</t>
+  </si>
+  <si>
+    <t>電車が遅いです。</t>
+  </si>
+  <si>
+    <t>Tàu điện bị muộn.</t>
+  </si>
+  <si>
+    <t>近い</t>
+  </si>
+  <si>
+    <t>ちかい</t>
+  </si>
+  <si>
+    <t>Gần</t>
+  </si>
+  <si>
+    <t>駅は近いです。</t>
+  </si>
+  <si>
+    <t>Nhà ga thì gần.</t>
+  </si>
+  <si>
+    <t>遠い</t>
+  </si>
+  <si>
+    <t>とおい</t>
+  </si>
+  <si>
+    <t>Xa</t>
+  </si>
+  <si>
+    <t>学校は遠いです。</t>
+  </si>
+  <si>
+    <t>Trường học thì xa.</t>
+  </si>
+  <si>
+    <t>暑い</t>
+  </si>
+  <si>
+    <t>あつい</t>
+  </si>
+  <si>
+    <t>Nóng (thời tiết)</t>
+  </si>
+  <si>
+    <t>今日はいです。</t>
+  </si>
+  <si>
+    <t>Hôm nay trời nóng.</t>
+  </si>
+  <si>
+    <t>寒い</t>
+  </si>
+  <si>
+    <t>さむい</t>
+  </si>
+  <si>
+    <t>Lạnh (thời tiết)</t>
+  </si>
+  <si>
+    <t>冬は寒いです。</t>
+  </si>
+  <si>
+    <t>Mùa đông thì lạnh.</t>
+  </si>
+  <si>
+    <t>暖かい</t>
+  </si>
+  <si>
+    <t>あたたかい</t>
+  </si>
+  <si>
+    <t>Ấm áp</t>
+  </si>
+  <si>
+    <t>春は暖かいです。</t>
+  </si>
+  <si>
+    <t>Mùa xuân ấm áp.</t>
+  </si>
+  <si>
+    <t>涼しい</t>
+  </si>
+  <si>
+    <t>すずしい</t>
+  </si>
+  <si>
+    <t>Mát mẻ</t>
+  </si>
+  <si>
+    <t>秋は涼しいです。</t>
+  </si>
+  <si>
+    <t>Mùa thu mát mẻ.</t>
+  </si>
+  <si>
+    <t>難しい</t>
+  </si>
+  <si>
+    <t>むずかしい</t>
+  </si>
+  <si>
+    <t>Khó</t>
+  </si>
+  <si>
+    <t>日本語は難しいです。</t>
+  </si>
+  <si>
+    <t>Tiếng Nhật khó.</t>
+  </si>
+  <si>
+    <t>易しい</t>
+  </si>
+  <si>
+    <t>やさしい</t>
+  </si>
+  <si>
+    <t>Dễ</t>
+  </si>
+  <si>
+    <t>この問題は易しいです。</t>
+  </si>
+  <si>
+    <t>Câu hỏi này dễ.</t>
+  </si>
+  <si>
+    <t>忙しい</t>
+  </si>
+  <si>
+    <t>いそがしい</t>
+  </si>
+  <si>
+    <t>Bận rộn</t>
+  </si>
+  <si>
+    <t>今日は忙しいです。</t>
+  </si>
+  <si>
+    <t>Hôm nay tôi bận.</t>
+  </si>
+  <si>
+    <t>親切</t>
+  </si>
+  <si>
+    <t>しんせつ</t>
+  </si>
+  <si>
+    <t>Thân thiện / Tốt bụng</t>
+  </si>
+  <si>
+    <t>先生は親切です。</t>
+  </si>
+  <si>
+    <t>Thầy giáo rất tốt bụng.</t>
+  </si>
+  <si>
+    <t>静か</t>
+  </si>
+  <si>
+    <t>しずか</t>
+  </si>
+  <si>
+    <t>Yên tĩnh</t>
+  </si>
+  <si>
+    <t>部屋は静かです。</t>
+  </si>
+  <si>
+    <t>Căn phòng yên tĩnh.</t>
+  </si>
+  <si>
+    <t>にぎやか</t>
+  </si>
+  <si>
+    <t>Nhộn nhịp</t>
+  </si>
+  <si>
+    <t>町はにぎやかです。</t>
+  </si>
+  <si>
+    <t>Thành phố nhộn nhịp.</t>
+  </si>
+  <si>
+    <t>猫</t>
+  </si>
+  <si>
+    <t>ねこ</t>
+  </si>
+  <si>
+    <t>Mèo</t>
+  </si>
+  <si>
+    <t>猫がいます。</t>
+  </si>
+  <si>
+    <t>Có một con mèo.</t>
+  </si>
+  <si>
+    <t>犬</t>
+  </si>
+  <si>
+    <t>いぬ</t>
+  </si>
+  <si>
+    <t>Chó</t>
+  </si>
+  <si>
+    <t>犬が好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích chó.</t>
+  </si>
+  <si>
+    <t>鳥</t>
+  </si>
+  <si>
+    <t>とり</t>
+  </si>
+  <si>
+    <t>Chim</t>
+  </si>
+  <si>
+    <t>鳥が飛んでいます。</t>
+  </si>
+  <si>
+    <t>Chim đang bay.</t>
+  </si>
+  <si>
+    <t>花</t>
+  </si>
+  <si>
+    <t>はな</t>
+  </si>
+  <si>
+    <t>Hoa</t>
+  </si>
+  <si>
+    <t>綺麗な花が咲いています。</t>
+  </si>
+  <si>
+    <t>Hoa đẹp đang nở.</t>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>き</t>
+  </si>
+  <si>
+    <t>Cây</t>
+  </si>
+  <si>
+    <t>大きい木があります。</t>
+  </si>
+  <si>
+    <t>Có một cái cây lớn.</t>
+  </si>
+  <si>
+    <t>雨</t>
+  </si>
+  <si>
+    <t>あめ</t>
+  </si>
+  <si>
+    <t>Mưa</t>
+  </si>
+  <si>
+    <t>雨が降っています。</t>
+  </si>
+  <si>
+    <t>Trời đang mưa.</t>
+  </si>
+  <si>
+    <t>雪</t>
+  </si>
+  <si>
+    <t>ゆき</t>
+  </si>
+  <si>
+    <t>Tuyết</t>
+  </si>
+  <si>
+    <t>雪が好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích tuyết.</t>
+  </si>
+  <si>
+    <t>風</t>
+  </si>
+  <si>
+    <t>かぜ</t>
+  </si>
+  <si>
+    <t>Gió</t>
+  </si>
+  <si>
+    <t>強い風が吹いています。</t>
+  </si>
+  <si>
+    <t>Gió mạnh đang thổi.</t>
+  </si>
+  <si>
+    <t>天気</t>
+  </si>
+  <si>
+    <t>てんき</t>
+  </si>
+  <si>
+    <t>Thời tiết</t>
+  </si>
+  <si>
+    <t>今日の天気はどうですか。</t>
+  </si>
+  <si>
+    <t>Thời tiết hôm nay thế nào?</t>
+  </si>
+  <si>
+    <t>太陽</t>
+  </si>
+  <si>
+    <t>たいよう</t>
+  </si>
+  <si>
+    <t>Mặt trời</t>
+  </si>
+  <si>
+    <t>太陽が登ります。</t>
+  </si>
+  <si>
+    <t>Mặt trời mọc.</t>
+  </si>
+  <si>
+    <t>月</t>
+  </si>
+  <si>
+    <t>つき</t>
+  </si>
+  <si>
+    <t>Mặt trăng</t>
+  </si>
+  <si>
+    <t>月がきれいです。</t>
+  </si>
+  <si>
+    <t>Mặt trăng đẹp.</t>
+  </si>
+  <si>
+    <t>星</t>
+  </si>
+  <si>
+    <t>ほし</t>
+  </si>
+  <si>
+    <t>Ngôi sao</t>
+  </si>
+  <si>
+    <t>星がたくさん見えます。</t>
+  </si>
+  <si>
+    <t>Thấy rất nhiều ngôi sao.</t>
+  </si>
+  <si>
+    <t>春</t>
+  </si>
+  <si>
+    <t>はる</t>
+  </si>
+  <si>
+    <t>Mùa xuân</t>
+  </si>
+  <si>
+    <t>春が好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích mùa xuân.</t>
+  </si>
+  <si>
+    <t>夏</t>
+  </si>
+  <si>
+    <t>なつ</t>
+  </si>
+  <si>
+    <t>Mùa hè</t>
+  </si>
+  <si>
+    <t>夏は暑いです。</t>
+  </si>
+  <si>
+    <t>Mùa hè thì nóng.</t>
+  </si>
+  <si>
+    <t>秋</t>
+  </si>
+  <si>
+    <t>あき</t>
+  </si>
+  <si>
+    <t>Mùa thu</t>
+  </si>
+  <si>
+    <t>秋になりました。</t>
+  </si>
+  <si>
+    <t>Đã sang mùa thu.</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>ふゆ</t>
+  </si>
+  <si>
+    <t>Mùa đông</t>
+  </si>
+  <si>
+    <t>駅</t>
+  </si>
+  <si>
+    <t>えき</t>
+  </si>
+  <si>
+    <t>Nhà ga</t>
+  </si>
+  <si>
+    <t>駅で友達に会います。</t>
+  </si>
+  <si>
+    <t>Gặp bạn ở nhà ga.</t>
+  </si>
+  <si>
+    <t>空港</t>
+  </si>
+  <si>
+    <t>くうこう</t>
+  </si>
+  <si>
+    <t>Sân bay</t>
+  </si>
+  <si>
+    <t>空港へ行きます。</t>
+  </si>
+  <si>
+    <t>Đi đến sân bay.</t>
+  </si>
+  <si>
+    <t>銀行</t>
+  </si>
+  <si>
+    <t>ぎんこう</t>
+  </si>
+  <si>
+    <t>Ngân hàng</t>
+  </si>
+  <si>
+    <t>銀行でお金を下ろします。</t>
+  </si>
+  <si>
+    <t>Rút tiền ở ngân hàng.</t>
+  </si>
+  <si>
+    <t>郵便局</t>
+  </si>
+  <si>
+    <t>ゆうびんきょく</t>
+  </si>
+  <si>
+    <t>Bưu điện</t>
+  </si>
+  <si>
+    <t>郵便局で切手を買います。</t>
+  </si>
+  <si>
+    <t>Mua tem ở bưu điện.</t>
+  </si>
+  <si>
+    <t>図書館</t>
+  </si>
+  <si>
+    <t>としょかん</t>
+  </si>
+  <si>
+    <t>Thư viện</t>
+  </si>
+  <si>
+    <t>図書館で本を借ります。</t>
+  </si>
+  <si>
+    <t>Mượn sách ở thư viện.</t>
+  </si>
+  <si>
+    <t>映画館</t>
+  </si>
+  <si>
+    <t>えいがかん</t>
+  </si>
+  <si>
+    <t>Rạp chiếu phim</t>
+  </si>
+  <si>
+    <t>映画館で映画を見ます。</t>
+  </si>
+  <si>
+    <t>Xem phim ở rạp.</t>
+  </si>
+  <si>
+    <t>公園</t>
+  </si>
+  <si>
+    <t>こうえん</t>
+  </si>
+  <si>
+    <t>Công viên</t>
+  </si>
+  <si>
+    <t>公園を散歩します。</t>
+  </si>
+  <si>
+    <t>Tản bộ ở công viên.</t>
+  </si>
+  <si>
+    <t>店</t>
+  </si>
+  <si>
+    <t>みせ</t>
+  </si>
+  <si>
+    <t>Cửa hàng</t>
+  </si>
+  <si>
+    <t>この店は有名です。</t>
+  </si>
+  <si>
+    <t>Cửa hàng này nổi tiếng.</t>
+  </si>
+  <si>
+    <t>スーパー</t>
+  </si>
+  <si>
+    <t>すーぱー</t>
+  </si>
+  <si>
+    <t>Siêu thị</t>
+  </si>
+  <si>
+    <t>スーパーで買い物をします。</t>
+  </si>
+  <si>
+    <t>Mua sắm ở siêu thị.</t>
+  </si>
+  <si>
+    <t>デパート</t>
+  </si>
+  <si>
+    <t>でぱーと</t>
+  </si>
+  <si>
+    <t>Trung tâm thương mại</t>
+  </si>
+  <si>
+    <t>デパートで服を買いました。</t>
+  </si>
+  <si>
+    <t>Tôi đã mua quần áo ở trung tâm thương mại.</t>
+  </si>
+  <si>
+    <t>レストラン</t>
+  </si>
+  <si>
+    <t>れすとらん</t>
+  </si>
+  <si>
+    <t>Nhà hàng</t>
+  </si>
+  <si>
+    <t>レストランでご飯を食べます。</t>
+  </si>
+  <si>
+    <t>Ăn cơm ở nhà hàng.</t>
+  </si>
+  <si>
+    <t>喫茶店</t>
+  </si>
+  <si>
+    <t>きっさてん</t>
+  </si>
+  <si>
+    <t>Quán cà phê</t>
+  </si>
+  <si>
+    <t>喫茶店でコーヒーを飲みます。</t>
+  </si>
+  <si>
+    <t>Uống cà phê ở quán cà phê.</t>
+  </si>
+  <si>
+    <t>ホテル</t>
+  </si>
+  <si>
+    <t>ほてる</t>
+  </si>
+  <si>
+    <t>Khách sạn</t>
+  </si>
+  <si>
+    <t>ホテルに泊まります。</t>
+  </si>
+  <si>
+    <t>Ở lại khách sạn.</t>
+  </si>
+  <si>
+    <t>バス</t>
+  </si>
+  <si>
+    <t>ばす</t>
+  </si>
+  <si>
+    <t>Xe buýt</t>
+  </si>
+  <si>
+    <t>バスに乗ります。</t>
+  </si>
+  <si>
+    <t>Đi xe buýt.</t>
+  </si>
+  <si>
+    <t>タクシー</t>
+  </si>
+  <si>
+    <t>たくしー</t>
+  </si>
+  <si>
+    <t>Xe taxi</t>
+  </si>
+  <si>
+    <t>タクシーを呼びます。</t>
+  </si>
+  <si>
+    <t>Gọi xe taxi.</t>
+  </si>
+  <si>
+    <t>飛行機</t>
+  </si>
+  <si>
+    <t>ひこうき</t>
+  </si>
+  <si>
+    <t>Máy bay</t>
+  </si>
+  <si>
+    <t>飛行機で行きます。</t>
+  </si>
+  <si>
+    <t>Đi bằng máy bay.</t>
+  </si>
+  <si>
+    <t>自転車</t>
+  </si>
+  <si>
+    <t>じてんしゃ</t>
+  </si>
+  <si>
+    <t>Xe đạp</t>
+  </si>
+  <si>
+    <t>自転車に乗ります。</t>
+  </si>
+  <si>
+    <t>Đi xe đạp.</t>
+  </si>
+  <si>
+    <t>切符</t>
+  </si>
+  <si>
+    <t>きっぷ</t>
+  </si>
+  <si>
+    <t>Vé</t>
+  </si>
+  <si>
+    <t>切符を買います。</t>
+  </si>
+  <si>
+    <t>Mua vé.</t>
+  </si>
+  <si>
+    <t>荷物</t>
+  </si>
+  <si>
+    <t>にもつ</t>
+  </si>
+  <si>
+    <t>Hành lý / Đồ đạc</t>
+  </si>
+  <si>
+    <t>荷物を持ちます。</t>
+  </si>
+  <si>
+    <t>Cầm hành lý.</t>
+  </si>
+  <si>
+    <t>お金</t>
+  </si>
+  <si>
+    <t>おかね</t>
+  </si>
+  <si>
+    <t>Tiền</t>
+  </si>
+  <si>
+    <t>お金があります。</t>
+  </si>
+  <si>
+    <t>Có tiền.</t>
+  </si>
+  <si>
+    <t>財布</t>
+  </si>
+  <si>
+    <t>さいふ</t>
+  </si>
+  <si>
+    <t>Ví tiền</t>
+  </si>
+  <si>
+    <t>財布を忘れました。</t>
+  </si>
+  <si>
+    <t>Tôi đã quên ví.</t>
+  </si>
+  <si>
+    <t>時計</t>
+  </si>
+  <si>
+    <t>とけい</t>
+  </si>
+  <si>
+    <t>Đồng hồ</t>
+  </si>
+  <si>
+    <t>新しい時計を買いました。</t>
+  </si>
+  <si>
+    <t>Tôi đã mua đồng hồ mới.</t>
+  </si>
+  <si>
+    <t>傘</t>
+  </si>
+  <si>
+    <t>かさ</t>
+  </si>
+  <si>
+    <t>Cây dù / Ô</t>
+  </si>
+  <si>
+    <t>傘をさします。</t>
+  </si>
+  <si>
+    <t>Che ô.</t>
+  </si>
+  <si>
+    <t>鞄</t>
+  </si>
+  <si>
+    <t>かばん</t>
+  </si>
+  <si>
+    <t>Cặp / Túi xách</t>
+  </si>
+  <si>
+    <t>大きい鞄です。</t>
+  </si>
+  <si>
+    <t>Cái cặp lớn.</t>
+  </si>
+  <si>
+    <t>靴</t>
+  </si>
+  <si>
+    <t>くつ</t>
+  </si>
+  <si>
+    <t>Giày</t>
+  </si>
+  <si>
+    <t>靴をはきます。</t>
+  </si>
+  <si>
+    <t>Đi giày.</t>
+  </si>
+  <si>
+    <t>服</t>
+  </si>
+  <si>
+    <t>ふく</t>
+  </si>
+  <si>
+    <t>Quần áo</t>
+  </si>
+  <si>
+    <t>服を着ます。</t>
+  </si>
+  <si>
+    <t>Mặc quần áo.</t>
+  </si>
+  <si>
+    <t>眼鏡</t>
+  </si>
+  <si>
+    <t>めがね</t>
+  </si>
+  <si>
+    <t>Kính mắt</t>
+  </si>
+  <si>
+    <t>眼鏡をかけます。</t>
+  </si>
+  <si>
+    <t>Đeo kính.</t>
+  </si>
+  <si>
+    <t>帽子</t>
+  </si>
+  <si>
+    <t>ぼうし</t>
+  </si>
+  <si>
+    <t>Mũ / Nón</t>
+  </si>
+  <si>
+    <t>帽子をかぶります。</t>
+  </si>
+  <si>
+    <t>Đội mũ.</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>しゃしん</t>
+  </si>
+  <si>
+    <t>Bức ảnh</t>
+  </si>
+  <si>
+    <t>写真を撮ります。</t>
+  </si>
+  <si>
+    <t>Chụp ảnh.</t>
+  </si>
+  <si>
+    <t>手紙</t>
+  </si>
+  <si>
+    <t>てがみ</t>
+  </si>
+  <si>
+    <t>Lá thư</t>
+  </si>
+  <si>
+    <t>手紙を出します。</t>
+  </si>
+  <si>
+    <t>Gửi thư.</t>
+  </si>
+  <si>
+    <t>電話</t>
+  </si>
+  <si>
+    <t>でんわ</t>
+  </si>
+  <si>
+    <t>Điện thoại</t>
+  </si>
+  <si>
+    <t>電話をかけます。</t>
+  </si>
+  <si>
+    <t>Gọi điện thoại.</t>
+  </si>
+  <si>
+    <t>電気</t>
+  </si>
+  <si>
+    <t>でんき</t>
+  </si>
+  <si>
+    <t>Điện / Đèn</t>
+  </si>
+  <si>
+    <t>電気をつけます。</t>
+  </si>
+  <si>
+    <t>鍵</t>
+  </si>
+  <si>
+    <t>かぎ</t>
+  </si>
+  <si>
+    <t>Chìa khóa</t>
+  </si>
+  <si>
+    <t>鍵をかけます。</t>
+  </si>
+  <si>
+    <t>Khóa cửa.</t>
+  </si>
+  <si>
+    <t>机</t>
+  </si>
+  <si>
+    <t>つくえ</t>
+  </si>
+  <si>
+    <t>Bàn</t>
+  </si>
+  <si>
+    <t>机の上に本があります。</t>
+  </si>
+  <si>
+    <t>Trên bàn có quyển sách.</t>
+  </si>
+  <si>
+    <t>椅子</t>
+  </si>
+  <si>
+    <t>いす</t>
+  </si>
+  <si>
+    <t>Ghế</t>
+  </si>
+  <si>
+    <t>椅子に座ってください。</t>
+  </si>
+  <si>
+    <t>Hãy ngồi xuống ghế.</t>
+  </si>
+  <si>
+    <t>窓</t>
+  </si>
+  <si>
+    <t>まど</t>
+  </si>
+  <si>
+    <t>Cửa sổ</t>
+  </si>
+  <si>
+    <t>窓を開けます。</t>
+  </si>
+  <si>
+    <t>Mở cửa sổ.</t>
+  </si>
+  <si>
+    <t>ドア</t>
+  </si>
+  <si>
+    <t>どあ</t>
+  </si>
+  <si>
+    <t>Cửa ra vào</t>
+  </si>
+  <si>
+    <t>ドアを閉めます。</t>
+  </si>
+  <si>
+    <t>Đóng cửa.</t>
+  </si>
+  <si>
+    <t>箱</t>
+  </si>
+  <si>
+    <t>はこ</t>
+  </si>
+  <si>
+    <t>Cái hộp</t>
+  </si>
+  <si>
+    <t>箱に入れます。</t>
+  </si>
+  <si>
+    <t>Cho vào hộp.</t>
+  </si>
+  <si>
+    <t>お茶</t>
+  </si>
+  <si>
+    <t>おちゃ</t>
+  </si>
+  <si>
+    <t>Trà / Chè</t>
+  </si>
+  <si>
+    <t>お茶を飲みましょう。</t>
+  </si>
+  <si>
+    <t>Cùng uống trà nào.</t>
+  </si>
+  <si>
+    <t>牛乳</t>
+  </si>
+  <si>
+    <t>ぎゅうにゅう</t>
+  </si>
+  <si>
+    <t>Sữa bò</t>
+  </si>
+  <si>
+    <t>牛乳を買いました。</t>
+  </si>
+  <si>
+    <t>Tôi đã mua sữa bò.</t>
+  </si>
+  <si>
+    <t>お酒</t>
+  </si>
+  <si>
+    <t>おさけ</t>
+  </si>
+  <si>
+    <t>Rượu</t>
+  </si>
+  <si>
+    <t>お酒を飲みません。</t>
+  </si>
+  <si>
+    <t>Tôi không uống rượu.</t>
+  </si>
+  <si>
+    <t>卵</t>
+  </si>
+  <si>
+    <t>たまご</t>
+  </si>
+  <si>
+    <t>Trứng</t>
+  </si>
+  <si>
+    <t>卵を食べます。</t>
+  </si>
+  <si>
+    <t>Ăn trứng.</t>
+  </si>
+  <si>
+    <t>野菜</t>
+  </si>
+  <si>
+    <t>やさい</t>
+  </si>
+  <si>
+    <t>Rau</t>
+  </si>
+  <si>
+    <t>野菜が好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích rau.</t>
+  </si>
+  <si>
+    <t>果物</t>
+  </si>
+  <si>
+    <t>くだもの</t>
+  </si>
+  <si>
+    <t>Hoa quả / Trái cây</t>
+  </si>
+  <si>
+    <t>果物を買います。</t>
+  </si>
+  <si>
+    <t>Mua trái cây.</t>
+  </si>
+  <si>
+    <t>りんご</t>
+  </si>
+  <si>
+    <t>Quả táo</t>
+  </si>
+  <si>
+    <t>りんごを食べます。</t>
+  </si>
+  <si>
+    <t>Ăn táo.</t>
+  </si>
+  <si>
+    <t>みかん</t>
+  </si>
+  <si>
+    <t>Quả quýt</t>
+  </si>
+  <si>
+    <t>みかんが好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích quýt.</t>
+  </si>
+  <si>
+    <t>パン</t>
+  </si>
+  <si>
+    <t>ぱん</t>
+  </si>
+  <si>
+    <t>Bánh mì</t>
+  </si>
+  <si>
+    <t>朝パンを食べます。</t>
+  </si>
+  <si>
+    <t>Sáng tôi ăn bánh mì.</t>
+  </si>
+  <si>
+    <t>砂糖</t>
+  </si>
+  <si>
+    <t>さとう</t>
+  </si>
+  <si>
+    <t>Đường</t>
+  </si>
+  <si>
+    <t>砂糖を入れます。</t>
+  </si>
+  <si>
+    <t>Cho đường vào.</t>
+  </si>
+  <si>
+    <t>塩</t>
+  </si>
+  <si>
+    <t>しお</t>
+  </si>
+  <si>
+    <t>Muối</t>
+  </si>
+  <si>
+    <t>塩を取ってください。</t>
+  </si>
+  <si>
+    <t>Lấy giùm tôi hũ muối.</t>
+  </si>
+  <si>
+    <t>醤油</t>
+  </si>
+  <si>
+    <t>しょうゆ</t>
+  </si>
+  <si>
+    <t>Nước tương</t>
+  </si>
+  <si>
+    <t>醤油をつけます。</t>
+  </si>
+  <si>
+    <t>Chấm nước tương.</t>
+  </si>
+  <si>
+    <t>朝ご飯</t>
+  </si>
+  <si>
+    <t>あさごはん</t>
+  </si>
+  <si>
+    <t>Bữa sáng</t>
+  </si>
+  <si>
+    <t>朝ご飯を食べましたか。</t>
+  </si>
+  <si>
+    <t>Bạn đã ăn sáng chưa?</t>
+  </si>
+  <si>
+    <t>昼ご飯</t>
+  </si>
+  <si>
+    <t>ひるごはん</t>
+  </si>
+  <si>
+    <t>Bữa trưa</t>
+  </si>
+  <si>
+    <t>一緒に昼ご飯を食べましょう。</t>
+  </si>
+  <si>
+    <t>Cùng ăn trưa nào.</t>
+  </si>
+  <si>
+    <t>晩ご飯</t>
+  </si>
+  <si>
+    <t>ばんごはん</t>
+  </si>
+  <si>
+    <t>Bữa tối</t>
+  </si>
+  <si>
+    <t>晩ご飯を作ります。</t>
+  </si>
+  <si>
+    <t>Nấu bữa tối.</t>
+  </si>
+  <si>
+    <t>弁当</t>
+  </si>
+  <si>
+    <t>べんとう</t>
+  </si>
+  <si>
+    <t>Cơm hộp</t>
+  </si>
+  <si>
+    <t>弁当を買います。</t>
+  </si>
+  <si>
+    <t>Mua cơm hộp.</t>
+  </si>
+  <si>
+    <t>歌</t>
+  </si>
+  <si>
+    <t>うた</t>
+  </si>
+  <si>
+    <t>Bài hát</t>
+  </si>
+  <si>
+    <t>歌を歌います。</t>
+  </si>
+  <si>
+    <t>Hát một bài hát.</t>
+  </si>
+  <si>
+    <t>音楽</t>
+  </si>
+  <si>
+    <t>おんがく</t>
+  </si>
+  <si>
+    <t>Âm nhạc</t>
+  </si>
+  <si>
+    <t>映画</t>
+  </si>
+  <si>
+    <t>えいが</t>
+  </si>
+  <si>
+    <t>Bộ phim</t>
+  </si>
+  <si>
+    <t>映画を見に行きます。</t>
+  </si>
+  <si>
+    <t>Đi xem phim.</t>
+  </si>
+  <si>
+    <t>スポーツ</t>
+  </si>
+  <si>
+    <t>すぽーつ</t>
+  </si>
+  <si>
+    <t>Thể thao</t>
+  </si>
+  <si>
+    <t>スポーツが好きです。</t>
+  </si>
+  <si>
+    <t>Tôi thích thể thao.</t>
+  </si>
+  <si>
+    <t>サッカー</t>
+  </si>
+  <si>
+    <t>さっかー</t>
+  </si>
+  <si>
+    <t>Bóng đá</t>
+  </si>
+  <si>
+    <t>サッカーをします。</t>
+  </si>
+  <si>
+    <t>Chơi bóng đá.</t>
+  </si>
+  <si>
+    <t>テニス</t>
+  </si>
+  <si>
+    <t>てにす</t>
+  </si>
+  <si>
+    <t>Quần vợt / Tennis</t>
+  </si>
+  <si>
+    <t>テニスを練習します。</t>
+  </si>
+  <si>
+    <t>Luyện tập tennis.</t>
+  </si>
+  <si>
+    <t>勉強</t>
+  </si>
+  <si>
+    <t>べんきょう</t>
+  </si>
+  <si>
+    <t>Học tập</t>
+  </si>
+  <si>
+    <t>毎日勉強します。</t>
+  </si>
+  <si>
+    <t>Học bài hàng ngày.</t>
+  </si>
+  <si>
+    <t>仕事</t>
+  </si>
+  <si>
+    <t>しごと</t>
+  </si>
+  <si>
+    <t>Công việc</t>
+  </si>
+  <si>
+    <t>仕事が終わりました。</t>
+  </si>
+  <si>
+    <t>Công việc đã xong.</t>
+  </si>
+  <si>
+    <t>買い物</t>
+  </si>
+  <si>
+    <t>かいもの</t>
+  </si>
+  <si>
+    <t>Mua sắm</t>
+  </si>
+  <si>
+    <t>買い物に行きます。</t>
+  </si>
+  <si>
+    <t>Đi mua sắm.</t>
+  </si>
+  <si>
+    <t>旅行</t>
+  </si>
+  <si>
+    <t>りょこう</t>
+  </si>
+  <si>
+    <t>Du lịch</t>
+  </si>
+  <si>
+    <t>日本へ旅行します。</t>
+  </si>
+  <si>
+    <t>Đi du lịch Nhật Bản.</t>
+  </si>
+  <si>
+    <t>散歩</t>
+  </si>
+  <si>
+    <t>さんぽ</t>
+  </si>
+  <si>
+    <t>Tản bộ</t>
+  </si>
+  <si>
+    <t>公園で散歩します。</t>
+  </si>
+  <si>
+    <t>Tản bộ trong công viên.</t>
+  </si>
+  <si>
+    <t>水泳</t>
+  </si>
+  <si>
+    <t>すいえい</t>
+  </si>
+  <si>
+    <t>Bơi lội</t>
+  </si>
+  <si>
+    <t>水泳が得意です。</t>
+  </si>
+  <si>
+    <t>Tôi giỏi bơi lội.</t>
+  </si>
+  <si>
+    <t>登る</t>
+  </si>
+  <si>
+    <t>のぼる</t>
+  </si>
+  <si>
+    <t>Leo / Trèo</t>
+  </si>
+  <si>
+    <t>山に登ります。</t>
+  </si>
+  <si>
+    <t>Leo núi.</t>
+  </si>
+  <si>
+    <t>浴びる</t>
+  </si>
+  <si>
+    <t>あびる</t>
+  </si>
+  <si>
+    <t>Tắm</t>
+  </si>
+  <si>
+    <t>シャワーを浴びます。</t>
+  </si>
+  <si>
+    <t>Tắm vòi hoa sen.</t>
+  </si>
+  <si>
+    <t>忘れる</t>
+  </si>
+  <si>
+    <t>わすれる</t>
+  </si>
+  <si>
+    <t>Quên</t>
+  </si>
+  <si>
+    <t>宿題を忘れました。</t>
+  </si>
+  <si>
+    <t>Tôi đã quên bài tập.</t>
+  </si>
+  <si>
+    <t>困る</t>
+  </si>
+  <si>
+    <t>こまる</t>
+  </si>
+  <si>
+    <t>Gặp khó khăn</t>
+  </si>
+  <si>
+    <t>お金がなくて困ります。</t>
+  </si>
+  <si>
+    <t>Không có tiền nên rất khó khăn.</t>
+  </si>
+  <si>
+    <t>頼む</t>
+  </si>
+  <si>
+    <t>たのむ</t>
+  </si>
+  <si>
+    <t>Nhờ vả</t>
+  </si>
+  <si>
+    <t>手伝いを頼みます。</t>
+  </si>
+  <si>
+    <t>Nhờ giúp đỡ.</t>
+  </si>
+  <si>
+    <t>手伝う</t>
+  </si>
+  <si>
+    <t>てつだう</t>
+  </si>
+  <si>
+    <t>Giúp đỡ</t>
+  </si>
+  <si>
+    <t>仕事を手伝います。</t>
+  </si>
+  <si>
+    <t>Giúp công việc.</t>
+  </si>
+  <si>
+    <t>渡す</t>
+  </si>
+  <si>
+    <t>わたす</t>
+  </si>
+  <si>
+    <t>Trao / Gửi</t>
+  </si>
+  <si>
+    <t>手紙を渡します。</t>
+  </si>
+  <si>
+    <t>Trao lá thư.</t>
+  </si>
+  <si>
+    <t>渡る</t>
+  </si>
+  <si>
+    <t>わたる</t>
+  </si>
+  <si>
+    <t>Băng qua</t>
+  </si>
+  <si>
+    <t>道を渡ります。</t>
+  </si>
+  <si>
+    <t>Băng qua đường.</t>
+  </si>
+  <si>
+    <t>曲がる</t>
+  </si>
+  <si>
+    <t>まがる</t>
+  </si>
+  <si>
+    <t>Rẽ / Cúi</t>
+  </si>
+  <si>
+    <t>右へ曲がります。</t>
+  </si>
+  <si>
+    <t>Rẽ bên phải.</t>
+  </si>
+  <si>
+    <t>止まる</t>
+  </si>
+  <si>
+    <t>とまる</t>
+  </si>
+  <si>
+    <t>Dừng lại</t>
+  </si>
+  <si>
+    <t>車が止まります。</t>
+  </si>
+  <si>
+    <t>Xe dừng lại.</t>
+  </si>
+  <si>
+    <t>降る</t>
+  </si>
+  <si>
+    <t>ふる</t>
+  </si>
+  <si>
+    <t>Rơi (mưa, tuyết)</t>
+  </si>
+  <si>
+    <t>雨が降ります。</t>
+  </si>
+  <si>
+    <t>Trời mưa.</t>
+  </si>
+  <si>
+    <t>脱ぐ</t>
+  </si>
+  <si>
+    <t>ぬぐ</t>
+  </si>
+  <si>
+    <t>Cởi (đồ)</t>
+  </si>
+  <si>
+    <t>靴を脱ぎます。</t>
+  </si>
+  <si>
+    <t>Cởi giày.</t>
+  </si>
+  <si>
+    <t>履く</t>
+  </si>
+  <si>
+    <t>はく</t>
+  </si>
+  <si>
+    <t>Đi / Mặc (giày, quần)</t>
+  </si>
+  <si>
+    <t>ズボンを履きます。</t>
+  </si>
+  <si>
+    <t>Mặc quần.</t>
+  </si>
+  <si>
+    <t>かぶる</t>
+  </si>
+  <si>
+    <t>Đội (mũ)</t>
+  </si>
+  <si>
+    <t>かける</t>
+  </si>
+  <si>
+    <t>Đeo (kính) / Gọi (điện)</t>
+  </si>
+  <si>
+    <t>磨く</t>
+  </si>
+  <si>
+    <t>みがく</t>
+  </si>
+  <si>
+    <t>Đánh (răng) / Chùi</t>
+  </si>
+  <si>
+    <t>歯を磨きます。</t>
+  </si>
+  <si>
+    <t>Đánh răng.</t>
+  </si>
+  <si>
+    <t>貼る</t>
+  </si>
+  <si>
+    <t>Dán</t>
+  </si>
+  <si>
+    <t>切手を貼ります。</t>
+  </si>
+  <si>
+    <t>Dán tem.</t>
+  </si>
+  <si>
+    <t>飾る</t>
+  </si>
+  <si>
+    <t>かざる</t>
+  </si>
+  <si>
+    <t>Trang trí</t>
+  </si>
+  <si>
+    <t>部屋に花を飾ります。</t>
+  </si>
+  <si>
+    <t>Trang trí hoa trong phòng.</t>
+  </si>
+  <si>
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>ExampleMeaning</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>海</t>
-  </si>
-  <si>
-    <t>うみ</t>
-  </si>
-  <si>
-    <t>Biển</t>
-  </si>
-  <si>
-    <t>川</t>
-  </si>
-  <si>
-    <t>かわ</t>
-  </si>
-  <si>
-    <t>Sông</t>
-  </si>
-  <si>
-    <t>空</t>
-  </si>
-  <si>
-    <t>そら</t>
-  </si>
-  <si>
-    <t>Bầu trời</t>
-  </si>
-  <si>
-    <t>山</t>
-  </si>
-  <si>
-    <t>やま</t>
-  </si>
-  <si>
-    <t>núi</t>
-  </si>
-  <si>
-    <t>私</t>
-  </si>
-  <si>
-    <t>わたし</t>
-  </si>
-  <si>
-    <t>tôi</t>
+    <t>Audio</t>
   </si>
 </sst>
 </file>
@@ -419,8 +3293,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24.77734375" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -430,63 +3310,85 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>977</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>978</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -496,27 +3398,3295 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D8" s="2"/>
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D9" s="2"/>
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" t="s">
+        <v>147</v>
+      </c>
+      <c r="E30" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" t="s">
+        <v>176</v>
+      </c>
+      <c r="D36" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" t="s">
+        <v>181</v>
+      </c>
+      <c r="D37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" t="s">
+        <v>191</v>
+      </c>
+      <c r="D39" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" t="s">
+        <v>206</v>
+      </c>
+      <c r="D42" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>209</v>
+      </c>
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" t="s">
+        <v>211</v>
+      </c>
+      <c r="D43" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" t="s">
+        <v>222</v>
+      </c>
+      <c r="E45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" t="s">
+        <v>227</v>
+      </c>
+      <c r="E46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>229</v>
+      </c>
+      <c r="B47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C47" t="s">
+        <v>231</v>
+      </c>
+      <c r="D47" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>234</v>
+      </c>
+      <c r="B48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" t="s">
+        <v>250</v>
+      </c>
+      <c r="C51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D51" t="s">
+        <v>252</v>
+      </c>
+      <c r="E51" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>254</v>
+      </c>
+      <c r="B52" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" t="s">
+        <v>257</v>
+      </c>
+      <c r="E52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>259</v>
+      </c>
+      <c r="B53" t="s">
+        <v>260</v>
+      </c>
+      <c r="C53" t="s">
+        <v>261</v>
+      </c>
+      <c r="D53" t="s">
+        <v>262</v>
+      </c>
+      <c r="E53" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>264</v>
+      </c>
+      <c r="B54" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" t="s">
+        <v>266</v>
+      </c>
+      <c r="D54" t="s">
+        <v>267</v>
+      </c>
+      <c r="E54" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>269</v>
+      </c>
+      <c r="B55" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" t="s">
+        <v>271</v>
+      </c>
+      <c r="D55" t="s">
+        <v>272</v>
+      </c>
+      <c r="E55" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>274</v>
+      </c>
+      <c r="B56" t="s">
+        <v>275</v>
+      </c>
+      <c r="C56" t="s">
+        <v>276</v>
+      </c>
+      <c r="D56" t="s">
+        <v>277</v>
+      </c>
+      <c r="E56" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>279</v>
+      </c>
+      <c r="B57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C57" t="s">
+        <v>281</v>
+      </c>
+      <c r="D57" t="s">
+        <v>282</v>
+      </c>
+      <c r="E57" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>284</v>
+      </c>
+      <c r="B58" t="s">
+        <v>285</v>
+      </c>
+      <c r="C58" t="s">
+        <v>286</v>
+      </c>
+      <c r="D58" t="s">
+        <v>287</v>
+      </c>
+      <c r="E58" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>289</v>
+      </c>
+      <c r="B59" t="s">
+        <v>290</v>
+      </c>
+      <c r="C59" t="s">
+        <v>291</v>
+      </c>
+      <c r="D59" t="s">
+        <v>292</v>
+      </c>
+      <c r="E59" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>294</v>
+      </c>
+      <c r="B60" t="s">
+        <v>295</v>
+      </c>
+      <c r="C60" t="s">
+        <v>296</v>
+      </c>
+      <c r="D60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E60" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>299</v>
+      </c>
+      <c r="B61" t="s">
+        <v>300</v>
+      </c>
+      <c r="C61" t="s">
+        <v>301</v>
+      </c>
+      <c r="D61" t="s">
+        <v>302</v>
+      </c>
+      <c r="E61" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>304</v>
+      </c>
+      <c r="B62" t="s">
+        <v>305</v>
+      </c>
+      <c r="C62" t="s">
+        <v>306</v>
+      </c>
+      <c r="D62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E62" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>309</v>
+      </c>
+      <c r="B63" t="s">
+        <v>310</v>
+      </c>
+      <c r="C63" t="s">
+        <v>311</v>
+      </c>
+      <c r="D63" t="s">
+        <v>247</v>
+      </c>
+      <c r="E63" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>313</v>
+      </c>
+      <c r="B64" t="s">
+        <v>314</v>
+      </c>
+      <c r="C64" t="s">
+        <v>315</v>
+      </c>
+      <c r="D64" t="s">
+        <v>316</v>
+      </c>
+      <c r="E64" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>318</v>
+      </c>
+      <c r="B65" t="s">
+        <v>319</v>
+      </c>
+      <c r="C65" t="s">
+        <v>320</v>
+      </c>
+      <c r="D65" t="s">
+        <v>321</v>
+      </c>
+      <c r="E65" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>323</v>
+      </c>
+      <c r="B66" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" t="s">
+        <v>325</v>
+      </c>
+      <c r="D66" t="s">
+        <v>326</v>
+      </c>
+      <c r="E66" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>328</v>
+      </c>
+      <c r="B67" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" t="s">
+        <v>330</v>
+      </c>
+      <c r="D67" t="s">
+        <v>331</v>
+      </c>
+      <c r="E67" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>333</v>
+      </c>
+      <c r="B68" t="s">
+        <v>334</v>
+      </c>
+      <c r="C68" t="s">
+        <v>335</v>
+      </c>
+      <c r="D68" t="s">
+        <v>336</v>
+      </c>
+      <c r="E68" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>338</v>
+      </c>
+      <c r="B69" t="s">
+        <v>339</v>
+      </c>
+      <c r="C69" t="s">
+        <v>340</v>
+      </c>
+      <c r="D69" t="s">
+        <v>341</v>
+      </c>
+      <c r="E69" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>343</v>
+      </c>
+      <c r="B70" t="s">
+        <v>344</v>
+      </c>
+      <c r="C70" t="s">
+        <v>345</v>
+      </c>
+      <c r="D70" t="s">
+        <v>346</v>
+      </c>
+      <c r="E70" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>348</v>
+      </c>
+      <c r="B71" t="s">
+        <v>349</v>
+      </c>
+      <c r="C71" t="s">
+        <v>350</v>
+      </c>
+      <c r="D71" t="s">
+        <v>351</v>
+      </c>
+      <c r="E71" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>353</v>
+      </c>
+      <c r="B72" t="s">
+        <v>354</v>
+      </c>
+      <c r="C72" t="s">
+        <v>355</v>
+      </c>
+      <c r="D72" t="s">
+        <v>356</v>
+      </c>
+      <c r="E72" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>358</v>
+      </c>
+      <c r="B73" t="s">
+        <v>359</v>
+      </c>
+      <c r="C73" t="s">
+        <v>360</v>
+      </c>
+      <c r="D73" t="s">
+        <v>361</v>
+      </c>
+      <c r="E73" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>363</v>
+      </c>
+      <c r="B74" t="s">
+        <v>364</v>
+      </c>
+      <c r="C74" t="s">
+        <v>365</v>
+      </c>
+      <c r="D74" t="s">
+        <v>366</v>
+      </c>
+      <c r="E74" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>368</v>
+      </c>
+      <c r="B75" t="s">
+        <v>369</v>
+      </c>
+      <c r="C75" t="s">
+        <v>370</v>
+      </c>
+      <c r="D75" t="s">
+        <v>371</v>
+      </c>
+      <c r="E75" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>373</v>
+      </c>
+      <c r="B76" t="s">
+        <v>374</v>
+      </c>
+      <c r="C76" t="s">
+        <v>375</v>
+      </c>
+      <c r="D76" t="s">
+        <v>376</v>
+      </c>
+      <c r="E76" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>378</v>
+      </c>
+      <c r="B77" t="s">
+        <v>379</v>
+      </c>
+      <c r="C77" t="s">
+        <v>380</v>
+      </c>
+      <c r="D77" t="s">
+        <v>381</v>
+      </c>
+      <c r="E77" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>383</v>
+      </c>
+      <c r="B78" t="s">
+        <v>384</v>
+      </c>
+      <c r="C78" t="s">
+        <v>385</v>
+      </c>
+      <c r="D78" t="s">
+        <v>386</v>
+      </c>
+      <c r="E78" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>388</v>
+      </c>
+      <c r="B79" t="s">
+        <v>389</v>
+      </c>
+      <c r="C79" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" t="s">
+        <v>391</v>
+      </c>
+      <c r="E79" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>393</v>
+      </c>
+      <c r="B80" t="s">
+        <v>394</v>
+      </c>
+      <c r="C80" t="s">
+        <v>395</v>
+      </c>
+      <c r="D80" t="s">
+        <v>396</v>
+      </c>
+      <c r="E80" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>398</v>
+      </c>
+      <c r="B81" t="s">
+        <v>399</v>
+      </c>
+      <c r="C81" t="s">
+        <v>400</v>
+      </c>
+      <c r="D81" t="s">
+        <v>401</v>
+      </c>
+      <c r="E81" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>403</v>
+      </c>
+      <c r="B82" t="s">
+        <v>403</v>
+      </c>
+      <c r="C82" t="s">
+        <v>404</v>
+      </c>
+      <c r="D82" t="s">
+        <v>405</v>
+      </c>
+      <c r="E82" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>407</v>
+      </c>
+      <c r="B83" t="s">
+        <v>408</v>
+      </c>
+      <c r="C83" t="s">
+        <v>409</v>
+      </c>
+      <c r="D83" t="s">
+        <v>410</v>
+      </c>
+      <c r="E83" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>412</v>
+      </c>
+      <c r="B84" t="s">
+        <v>413</v>
+      </c>
+      <c r="C84" t="s">
+        <v>414</v>
+      </c>
+      <c r="D84" t="s">
+        <v>415</v>
+      </c>
+      <c r="E84" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>417</v>
+      </c>
+      <c r="B85" t="s">
+        <v>418</v>
+      </c>
+      <c r="C85" t="s">
+        <v>419</v>
+      </c>
+      <c r="D85" t="s">
+        <v>420</v>
+      </c>
+      <c r="E85" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>422</v>
+      </c>
+      <c r="B86" t="s">
+        <v>423</v>
+      </c>
+      <c r="C86" t="s">
+        <v>424</v>
+      </c>
+      <c r="D86" t="s">
+        <v>425</v>
+      </c>
+      <c r="E86" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>427</v>
+      </c>
+      <c r="B87" t="s">
+        <v>428</v>
+      </c>
+      <c r="C87" t="s">
+        <v>429</v>
+      </c>
+      <c r="D87" t="s">
+        <v>430</v>
+      </c>
+      <c r="E87" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>432</v>
+      </c>
+      <c r="B88" t="s">
+        <v>433</v>
+      </c>
+      <c r="C88" t="s">
+        <v>434</v>
+      </c>
+      <c r="D88" t="s">
+        <v>435</v>
+      </c>
+      <c r="E88" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>437</v>
+      </c>
+      <c r="B89" t="s">
+        <v>438</v>
+      </c>
+      <c r="C89" t="s">
+        <v>439</v>
+      </c>
+      <c r="D89" t="s">
+        <v>440</v>
+      </c>
+      <c r="E89" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>442</v>
+      </c>
+      <c r="B90" t="s">
+        <v>443</v>
+      </c>
+      <c r="C90" t="s">
+        <v>444</v>
+      </c>
+      <c r="D90" t="s">
+        <v>445</v>
+      </c>
+      <c r="E90" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>447</v>
+      </c>
+      <c r="B91" t="s">
+        <v>448</v>
+      </c>
+      <c r="C91" t="s">
+        <v>449</v>
+      </c>
+      <c r="D91" t="s">
+        <v>450</v>
+      </c>
+      <c r="E91" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>452</v>
+      </c>
+      <c r="B92" t="s">
+        <v>453</v>
+      </c>
+      <c r="C92" t="s">
+        <v>454</v>
+      </c>
+      <c r="D92" t="s">
+        <v>455</v>
+      </c>
+      <c r="E92" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>457</v>
+      </c>
+      <c r="B93" t="s">
+        <v>458</v>
+      </c>
+      <c r="C93" t="s">
+        <v>459</v>
+      </c>
+      <c r="D93" t="s">
+        <v>460</v>
+      </c>
+      <c r="E93" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>462</v>
+      </c>
+      <c r="B94" t="s">
+        <v>463</v>
+      </c>
+      <c r="C94" t="s">
+        <v>464</v>
+      </c>
+      <c r="D94" t="s">
+        <v>465</v>
+      </c>
+      <c r="E94" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>467</v>
+      </c>
+      <c r="B95" t="s">
+        <v>468</v>
+      </c>
+      <c r="C95" t="s">
+        <v>469</v>
+      </c>
+      <c r="D95" t="s">
+        <v>470</v>
+      </c>
+      <c r="E95" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>472</v>
+      </c>
+      <c r="B96" t="s">
+        <v>473</v>
+      </c>
+      <c r="C96" t="s">
+        <v>474</v>
+      </c>
+      <c r="D96" t="s">
+        <v>475</v>
+      </c>
+      <c r="E96" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>477</v>
+      </c>
+      <c r="B97" t="s">
+        <v>478</v>
+      </c>
+      <c r="C97" t="s">
+        <v>479</v>
+      </c>
+      <c r="D97" t="s">
+        <v>480</v>
+      </c>
+      <c r="E97" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>482</v>
+      </c>
+      <c r="B98" t="s">
+        <v>483</v>
+      </c>
+      <c r="C98" t="s">
+        <v>484</v>
+      </c>
+      <c r="D98" t="s">
+        <v>485</v>
+      </c>
+      <c r="E98" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>487</v>
+      </c>
+      <c r="B99" t="s">
+        <v>487</v>
+      </c>
+      <c r="C99" t="s">
+        <v>488</v>
+      </c>
+      <c r="D99" t="s">
+        <v>489</v>
+      </c>
+      <c r="E99" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>491</v>
+      </c>
+      <c r="B100" t="s">
+        <v>492</v>
+      </c>
+      <c r="C100" t="s">
+        <v>493</v>
+      </c>
+      <c r="D100" t="s">
+        <v>494</v>
+      </c>
+      <c r="E100" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>496</v>
+      </c>
+      <c r="B101" t="s">
+        <v>497</v>
+      </c>
+      <c r="C101" t="s">
+        <v>498</v>
+      </c>
+      <c r="D101" t="s">
+        <v>499</v>
+      </c>
+      <c r="E101" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>501</v>
+      </c>
+      <c r="B102" t="s">
+        <v>502</v>
+      </c>
+      <c r="C102" t="s">
+        <v>503</v>
+      </c>
+      <c r="D102" t="s">
+        <v>504</v>
+      </c>
+      <c r="E102" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>506</v>
+      </c>
+      <c r="B103" t="s">
+        <v>507</v>
+      </c>
+      <c r="C103" t="s">
+        <v>508</v>
+      </c>
+      <c r="D103" t="s">
+        <v>509</v>
+      </c>
+      <c r="E103" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>511</v>
+      </c>
+      <c r="B104" t="s">
+        <v>512</v>
+      </c>
+      <c r="C104" t="s">
+        <v>513</v>
+      </c>
+      <c r="D104" t="s">
+        <v>514</v>
+      </c>
+      <c r="E104" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>516</v>
+      </c>
+      <c r="B105" t="s">
+        <v>517</v>
+      </c>
+      <c r="C105" t="s">
+        <v>518</v>
+      </c>
+      <c r="D105" t="s">
+        <v>519</v>
+      </c>
+      <c r="E105" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>521</v>
+      </c>
+      <c r="B106" t="s">
+        <v>522</v>
+      </c>
+      <c r="C106" t="s">
+        <v>523</v>
+      </c>
+      <c r="D106" t="s">
+        <v>524</v>
+      </c>
+      <c r="E106" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>526</v>
+      </c>
+      <c r="B107" t="s">
+        <v>527</v>
+      </c>
+      <c r="C107" t="s">
+        <v>528</v>
+      </c>
+      <c r="D107" t="s">
+        <v>529</v>
+      </c>
+      <c r="E107" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>531</v>
+      </c>
+      <c r="B108" t="s">
+        <v>532</v>
+      </c>
+      <c r="C108" t="s">
+        <v>533</v>
+      </c>
+      <c r="D108" t="s">
+        <v>534</v>
+      </c>
+      <c r="E108" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>536</v>
+      </c>
+      <c r="B109" t="s">
+        <v>537</v>
+      </c>
+      <c r="C109" t="s">
+        <v>538</v>
+      </c>
+      <c r="D109" t="s">
+        <v>539</v>
+      </c>
+      <c r="E109" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>541</v>
+      </c>
+      <c r="B110" t="s">
+        <v>542</v>
+      </c>
+      <c r="C110" t="s">
+        <v>543</v>
+      </c>
+      <c r="D110" t="s">
+        <v>544</v>
+      </c>
+      <c r="E110" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>546</v>
+      </c>
+      <c r="B111" t="s">
+        <v>547</v>
+      </c>
+      <c r="C111" t="s">
+        <v>548</v>
+      </c>
+      <c r="D111" t="s">
+        <v>549</v>
+      </c>
+      <c r="E111" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>551</v>
+      </c>
+      <c r="B112" t="s">
+        <v>552</v>
+      </c>
+      <c r="C112" t="s">
+        <v>553</v>
+      </c>
+      <c r="D112" t="s">
+        <v>554</v>
+      </c>
+      <c r="E112" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>556</v>
+      </c>
+      <c r="B113" t="s">
+        <v>557</v>
+      </c>
+      <c r="C113" t="s">
+        <v>558</v>
+      </c>
+      <c r="D113" t="s">
+        <v>559</v>
+      </c>
+      <c r="E113" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>561</v>
+      </c>
+      <c r="B114" t="s">
+        <v>562</v>
+      </c>
+      <c r="C114" t="s">
+        <v>563</v>
+      </c>
+      <c r="D114" t="s">
+        <v>564</v>
+      </c>
+      <c r="E114" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>566</v>
+      </c>
+      <c r="B115" t="s">
+        <v>567</v>
+      </c>
+      <c r="C115" t="s">
+        <v>568</v>
+      </c>
+      <c r="D115" t="s">
+        <v>450</v>
+      </c>
+      <c r="E115" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>569</v>
+      </c>
+      <c r="B116" t="s">
+        <v>570</v>
+      </c>
+      <c r="C116" t="s">
+        <v>571</v>
+      </c>
+      <c r="D116" t="s">
+        <v>572</v>
+      </c>
+      <c r="E116" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>574</v>
+      </c>
+      <c r="B117" t="s">
+        <v>575</v>
+      </c>
+      <c r="C117" t="s">
+        <v>576</v>
+      </c>
+      <c r="D117" t="s">
+        <v>577</v>
+      </c>
+      <c r="E117" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>579</v>
+      </c>
+      <c r="B118" t="s">
+        <v>580</v>
+      </c>
+      <c r="C118" t="s">
+        <v>581</v>
+      </c>
+      <c r="D118" t="s">
+        <v>582</v>
+      </c>
+      <c r="E118" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>584</v>
+      </c>
+      <c r="B119" t="s">
+        <v>585</v>
+      </c>
+      <c r="C119" t="s">
+        <v>586</v>
+      </c>
+      <c r="D119" t="s">
+        <v>587</v>
+      </c>
+      <c r="E119" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>589</v>
+      </c>
+      <c r="B120" t="s">
+        <v>590</v>
+      </c>
+      <c r="C120" t="s">
+        <v>591</v>
+      </c>
+      <c r="D120" t="s">
+        <v>592</v>
+      </c>
+      <c r="E120" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>594</v>
+      </c>
+      <c r="B121" t="s">
+        <v>595</v>
+      </c>
+      <c r="C121" t="s">
+        <v>596</v>
+      </c>
+      <c r="D121" t="s">
+        <v>597</v>
+      </c>
+      <c r="E121" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>599</v>
+      </c>
+      <c r="B122" t="s">
+        <v>600</v>
+      </c>
+      <c r="C122" t="s">
+        <v>601</v>
+      </c>
+      <c r="D122" t="s">
+        <v>602</v>
+      </c>
+      <c r="E122" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>604</v>
+      </c>
+      <c r="B123" t="s">
+        <v>605</v>
+      </c>
+      <c r="C123" t="s">
+        <v>606</v>
+      </c>
+      <c r="D123" t="s">
+        <v>607</v>
+      </c>
+      <c r="E123" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>609</v>
+      </c>
+      <c r="B124" t="s">
+        <v>610</v>
+      </c>
+      <c r="C124" t="s">
+        <v>611</v>
+      </c>
+      <c r="D124" t="s">
+        <v>612</v>
+      </c>
+      <c r="E124" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>614</v>
+      </c>
+      <c r="B125" t="s">
+        <v>615</v>
+      </c>
+      <c r="C125" t="s">
+        <v>616</v>
+      </c>
+      <c r="D125" t="s">
+        <v>617</v>
+      </c>
+      <c r="E125" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>619</v>
+      </c>
+      <c r="B126" t="s">
+        <v>620</v>
+      </c>
+      <c r="C126" t="s">
+        <v>621</v>
+      </c>
+      <c r="D126" t="s">
+        <v>622</v>
+      </c>
+      <c r="E126" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>624</v>
+      </c>
+      <c r="B127" t="s">
+        <v>625</v>
+      </c>
+      <c r="C127" t="s">
+        <v>626</v>
+      </c>
+      <c r="D127" t="s">
+        <v>627</v>
+      </c>
+      <c r="E127" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>629</v>
+      </c>
+      <c r="B128" t="s">
+        <v>630</v>
+      </c>
+      <c r="C128" t="s">
+        <v>631</v>
+      </c>
+      <c r="D128" t="s">
+        <v>632</v>
+      </c>
+      <c r="E128" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>634</v>
+      </c>
+      <c r="B129" t="s">
+        <v>635</v>
+      </c>
+      <c r="C129" t="s">
+        <v>636</v>
+      </c>
+      <c r="D129" t="s">
+        <v>637</v>
+      </c>
+      <c r="E129" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>639</v>
+      </c>
+      <c r="B130" t="s">
+        <v>640</v>
+      </c>
+      <c r="C130" t="s">
+        <v>641</v>
+      </c>
+      <c r="D130" t="s">
+        <v>642</v>
+      </c>
+      <c r="E130" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>644</v>
+      </c>
+      <c r="B131" t="s">
+        <v>645</v>
+      </c>
+      <c r="C131" t="s">
+        <v>646</v>
+      </c>
+      <c r="D131" t="s">
+        <v>647</v>
+      </c>
+      <c r="E131" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>649</v>
+      </c>
+      <c r="B132" t="s">
+        <v>650</v>
+      </c>
+      <c r="C132" t="s">
+        <v>651</v>
+      </c>
+      <c r="D132" t="s">
+        <v>652</v>
+      </c>
+      <c r="E132" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>654</v>
+      </c>
+      <c r="B133" t="s">
+        <v>655</v>
+      </c>
+      <c r="C133" t="s">
+        <v>656</v>
+      </c>
+      <c r="D133" t="s">
+        <v>657</v>
+      </c>
+      <c r="E133" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>659</v>
+      </c>
+      <c r="B134" t="s">
+        <v>660</v>
+      </c>
+      <c r="C134" t="s">
+        <v>661</v>
+      </c>
+      <c r="D134" t="s">
+        <v>662</v>
+      </c>
+      <c r="E134" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>664</v>
+      </c>
+      <c r="B135" t="s">
+        <v>665</v>
+      </c>
+      <c r="C135" t="s">
+        <v>666</v>
+      </c>
+      <c r="D135" t="s">
+        <v>667</v>
+      </c>
+      <c r="E135" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>669</v>
+      </c>
+      <c r="B136" t="s">
+        <v>670</v>
+      </c>
+      <c r="C136" t="s">
+        <v>671</v>
+      </c>
+      <c r="D136" t="s">
+        <v>672</v>
+      </c>
+      <c r="E136" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>674</v>
+      </c>
+      <c r="B137" t="s">
+        <v>675</v>
+      </c>
+      <c r="C137" t="s">
+        <v>676</v>
+      </c>
+      <c r="D137" t="s">
+        <v>677</v>
+      </c>
+      <c r="E137" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>679</v>
+      </c>
+      <c r="B138" t="s">
+        <v>680</v>
+      </c>
+      <c r="C138" t="s">
+        <v>681</v>
+      </c>
+      <c r="D138" t="s">
+        <v>682</v>
+      </c>
+      <c r="E138" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>684</v>
+      </c>
+      <c r="B139" t="s">
+        <v>685</v>
+      </c>
+      <c r="C139" t="s">
+        <v>686</v>
+      </c>
+      <c r="D139" t="s">
+        <v>687</v>
+      </c>
+      <c r="E139" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>689</v>
+      </c>
+      <c r="B140" t="s">
+        <v>690</v>
+      </c>
+      <c r="C140" t="s">
+        <v>691</v>
+      </c>
+      <c r="D140" t="s">
+        <v>692</v>
+      </c>
+      <c r="E140" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>694</v>
+      </c>
+      <c r="B141" t="s">
+        <v>695</v>
+      </c>
+      <c r="C141" t="s">
+        <v>696</v>
+      </c>
+      <c r="D141" t="s">
+        <v>697</v>
+      </c>
+      <c r="E141" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>699</v>
+      </c>
+      <c r="B142" t="s">
+        <v>700</v>
+      </c>
+      <c r="C142" t="s">
+        <v>701</v>
+      </c>
+      <c r="D142" t="s">
+        <v>702</v>
+      </c>
+      <c r="E142" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>704</v>
+      </c>
+      <c r="B143" t="s">
+        <v>705</v>
+      </c>
+      <c r="C143" t="s">
+        <v>706</v>
+      </c>
+      <c r="D143" t="s">
+        <v>707</v>
+      </c>
+      <c r="E143" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>709</v>
+      </c>
+      <c r="B144" t="s">
+        <v>710</v>
+      </c>
+      <c r="C144" t="s">
+        <v>711</v>
+      </c>
+      <c r="D144" t="s">
+        <v>712</v>
+      </c>
+      <c r="E144" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>714</v>
+      </c>
+      <c r="B145" t="s">
+        <v>715</v>
+      </c>
+      <c r="C145" t="s">
+        <v>716</v>
+      </c>
+      <c r="D145" t="s">
+        <v>717</v>
+      </c>
+      <c r="E145" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>719</v>
+      </c>
+      <c r="B146" t="s">
+        <v>720</v>
+      </c>
+      <c r="C146" t="s">
+        <v>721</v>
+      </c>
+      <c r="D146" t="s">
+        <v>722</v>
+      </c>
+      <c r="E146" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>724</v>
+      </c>
+      <c r="B147" t="s">
+        <v>725</v>
+      </c>
+      <c r="C147" t="s">
+        <v>726</v>
+      </c>
+      <c r="D147" t="s">
+        <v>727</v>
+      </c>
+      <c r="E147" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>728</v>
+      </c>
+      <c r="B148" t="s">
+        <v>729</v>
+      </c>
+      <c r="C148" t="s">
+        <v>730</v>
+      </c>
+      <c r="D148" t="s">
+        <v>731</v>
+      </c>
+      <c r="E148" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>733</v>
+      </c>
+      <c r="B149" t="s">
+        <v>734</v>
+      </c>
+      <c r="C149" t="s">
+        <v>735</v>
+      </c>
+      <c r="D149" t="s">
+        <v>736</v>
+      </c>
+      <c r="E149" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>738</v>
+      </c>
+      <c r="B150" t="s">
+        <v>739</v>
+      </c>
+      <c r="C150" t="s">
+        <v>740</v>
+      </c>
+      <c r="D150" t="s">
+        <v>741</v>
+      </c>
+      <c r="E150" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>743</v>
+      </c>
+      <c r="B151" t="s">
+        <v>744</v>
+      </c>
+      <c r="C151" t="s">
+        <v>745</v>
+      </c>
+      <c r="D151" t="s">
+        <v>746</v>
+      </c>
+      <c r="E151" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>748</v>
+      </c>
+      <c r="B152" t="s">
+        <v>749</v>
+      </c>
+      <c r="C152" t="s">
+        <v>750</v>
+      </c>
+      <c r="D152" t="s">
+        <v>751</v>
+      </c>
+      <c r="E152" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>753</v>
+      </c>
+      <c r="B153" t="s">
+        <v>754</v>
+      </c>
+      <c r="C153" t="s">
+        <v>755</v>
+      </c>
+      <c r="D153" t="s">
+        <v>756</v>
+      </c>
+      <c r="E153" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>758</v>
+      </c>
+      <c r="B154" t="s">
+        <v>759</v>
+      </c>
+      <c r="C154" t="s">
+        <v>760</v>
+      </c>
+      <c r="D154" t="s">
+        <v>761</v>
+      </c>
+      <c r="E154" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>763</v>
+      </c>
+      <c r="B155" t="s">
+        <v>764</v>
+      </c>
+      <c r="C155" t="s">
+        <v>765</v>
+      </c>
+      <c r="D155" t="s">
+        <v>766</v>
+      </c>
+      <c r="E155" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>768</v>
+      </c>
+      <c r="B156" t="s">
+        <v>769</v>
+      </c>
+      <c r="C156" t="s">
+        <v>770</v>
+      </c>
+      <c r="D156" t="s">
+        <v>771</v>
+      </c>
+      <c r="E156" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>773</v>
+      </c>
+      <c r="B157" t="s">
+        <v>774</v>
+      </c>
+      <c r="C157" t="s">
+        <v>775</v>
+      </c>
+      <c r="D157" t="s">
+        <v>776</v>
+      </c>
+      <c r="E157" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>778</v>
+      </c>
+      <c r="B158" t="s">
+        <v>779</v>
+      </c>
+      <c r="C158" t="s">
+        <v>780</v>
+      </c>
+      <c r="D158" t="s">
+        <v>781</v>
+      </c>
+      <c r="E158" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>783</v>
+      </c>
+      <c r="B159" t="s">
+        <v>784</v>
+      </c>
+      <c r="C159" t="s">
+        <v>785</v>
+      </c>
+      <c r="D159" t="s">
+        <v>786</v>
+      </c>
+      <c r="E159" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>788</v>
+      </c>
+      <c r="B160" t="s">
+        <v>788</v>
+      </c>
+      <c r="C160" t="s">
+        <v>789</v>
+      </c>
+      <c r="D160" t="s">
+        <v>790</v>
+      </c>
+      <c r="E160" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>792</v>
+      </c>
+      <c r="B161" t="s">
+        <v>792</v>
+      </c>
+      <c r="C161" t="s">
+        <v>793</v>
+      </c>
+      <c r="D161" t="s">
+        <v>794</v>
+      </c>
+      <c r="E161" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>796</v>
+      </c>
+      <c r="B162" t="s">
+        <v>797</v>
+      </c>
+      <c r="C162" t="s">
+        <v>798</v>
+      </c>
+      <c r="D162" t="s">
+        <v>799</v>
+      </c>
+      <c r="E162" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>801</v>
+      </c>
+      <c r="B163" t="s">
+        <v>802</v>
+      </c>
+      <c r="C163" t="s">
+        <v>803</v>
+      </c>
+      <c r="D163" t="s">
+        <v>804</v>
+      </c>
+      <c r="E163" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>806</v>
+      </c>
+      <c r="B164" t="s">
+        <v>807</v>
+      </c>
+      <c r="C164" t="s">
+        <v>808</v>
+      </c>
+      <c r="D164" t="s">
+        <v>809</v>
+      </c>
+      <c r="E164" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>811</v>
+      </c>
+      <c r="B165" t="s">
+        <v>812</v>
+      </c>
+      <c r="C165" t="s">
+        <v>813</v>
+      </c>
+      <c r="D165" t="s">
+        <v>814</v>
+      </c>
+      <c r="E165" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>816</v>
+      </c>
+      <c r="B166" t="s">
+        <v>817</v>
+      </c>
+      <c r="C166" t="s">
+        <v>818</v>
+      </c>
+      <c r="D166" t="s">
+        <v>819</v>
+      </c>
+      <c r="E166" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>821</v>
+      </c>
+      <c r="B167" t="s">
+        <v>822</v>
+      </c>
+      <c r="C167" t="s">
+        <v>823</v>
+      </c>
+      <c r="D167" t="s">
+        <v>824</v>
+      </c>
+      <c r="E167" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>826</v>
+      </c>
+      <c r="B168" t="s">
+        <v>827</v>
+      </c>
+      <c r="C168" t="s">
+        <v>828</v>
+      </c>
+      <c r="D168" t="s">
+        <v>829</v>
+      </c>
+      <c r="E168" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>831</v>
+      </c>
+      <c r="B169" t="s">
+        <v>832</v>
+      </c>
+      <c r="C169" t="s">
+        <v>833</v>
+      </c>
+      <c r="D169" t="s">
+        <v>834</v>
+      </c>
+      <c r="E169" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>836</v>
+      </c>
+      <c r="B170" t="s">
+        <v>837</v>
+      </c>
+      <c r="C170" t="s">
+        <v>838</v>
+      </c>
+      <c r="D170" t="s">
+        <v>839</v>
+      </c>
+      <c r="E170" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>841</v>
+      </c>
+      <c r="B171" t="s">
+        <v>842</v>
+      </c>
+      <c r="C171" t="s">
+        <v>843</v>
+      </c>
+      <c r="D171" t="s">
+        <v>162</v>
+      </c>
+      <c r="E171" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>844</v>
+      </c>
+      <c r="B172" t="s">
+        <v>845</v>
+      </c>
+      <c r="C172" t="s">
+        <v>846</v>
+      </c>
+      <c r="D172" t="s">
+        <v>847</v>
+      </c>
+      <c r="E172" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>849</v>
+      </c>
+      <c r="B173" t="s">
+        <v>850</v>
+      </c>
+      <c r="C173" t="s">
+        <v>851</v>
+      </c>
+      <c r="D173" t="s">
+        <v>852</v>
+      </c>
+      <c r="E173" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>854</v>
+      </c>
+      <c r="B174" t="s">
+        <v>855</v>
+      </c>
+      <c r="C174" t="s">
+        <v>856</v>
+      </c>
+      <c r="D174" t="s">
+        <v>857</v>
+      </c>
+      <c r="E174" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>859</v>
+      </c>
+      <c r="B175" t="s">
+        <v>860</v>
+      </c>
+      <c r="C175" t="s">
+        <v>861</v>
+      </c>
+      <c r="D175" t="s">
+        <v>862</v>
+      </c>
+      <c r="E175" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>864</v>
+      </c>
+      <c r="B176" t="s">
+        <v>865</v>
+      </c>
+      <c r="C176" t="s">
+        <v>866</v>
+      </c>
+      <c r="D176" t="s">
+        <v>867</v>
+      </c>
+      <c r="E176" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>869</v>
+      </c>
+      <c r="B177" t="s">
+        <v>870</v>
+      </c>
+      <c r="C177" t="s">
+        <v>871</v>
+      </c>
+      <c r="D177" t="s">
+        <v>872</v>
+      </c>
+      <c r="E177" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>874</v>
+      </c>
+      <c r="B178" t="s">
+        <v>875</v>
+      </c>
+      <c r="C178" t="s">
+        <v>876</v>
+      </c>
+      <c r="D178" t="s">
+        <v>877</v>
+      </c>
+      <c r="E178" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>879</v>
+      </c>
+      <c r="B179" t="s">
+        <v>880</v>
+      </c>
+      <c r="C179" t="s">
+        <v>881</v>
+      </c>
+      <c r="D179" t="s">
+        <v>882</v>
+      </c>
+      <c r="E179" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>884</v>
+      </c>
+      <c r="B180" t="s">
+        <v>885</v>
+      </c>
+      <c r="C180" t="s">
+        <v>886</v>
+      </c>
+      <c r="D180" t="s">
+        <v>887</v>
+      </c>
+      <c r="E180" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>889</v>
+      </c>
+      <c r="B181" t="s">
+        <v>890</v>
+      </c>
+      <c r="C181" t="s">
+        <v>891</v>
+      </c>
+      <c r="D181" t="s">
+        <v>892</v>
+      </c>
+      <c r="E181" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>894</v>
+      </c>
+      <c r="B182" t="s">
+        <v>895</v>
+      </c>
+      <c r="C182" t="s">
+        <v>896</v>
+      </c>
+      <c r="D182" t="s">
+        <v>897</v>
+      </c>
+      <c r="E182" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>899</v>
+      </c>
+      <c r="B183" t="s">
+        <v>900</v>
+      </c>
+      <c r="C183" t="s">
+        <v>901</v>
+      </c>
+      <c r="D183" t="s">
+        <v>902</v>
+      </c>
+      <c r="E183" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>904</v>
+      </c>
+      <c r="B184" t="s">
+        <v>905</v>
+      </c>
+      <c r="C184" t="s">
+        <v>906</v>
+      </c>
+      <c r="D184" t="s">
+        <v>907</v>
+      </c>
+      <c r="E184" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>909</v>
+      </c>
+      <c r="B185" t="s">
+        <v>910</v>
+      </c>
+      <c r="C185" t="s">
+        <v>911</v>
+      </c>
+      <c r="D185" t="s">
+        <v>912</v>
+      </c>
+      <c r="E185" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>914</v>
+      </c>
+      <c r="B186" t="s">
+        <v>915</v>
+      </c>
+      <c r="C186" t="s">
+        <v>916</v>
+      </c>
+      <c r="D186" t="s">
+        <v>917</v>
+      </c>
+      <c r="E186" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>919</v>
+      </c>
+      <c r="B187" t="s">
+        <v>920</v>
+      </c>
+      <c r="C187" t="s">
+        <v>921</v>
+      </c>
+      <c r="D187" t="s">
+        <v>922</v>
+      </c>
+      <c r="E187" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>924</v>
+      </c>
+      <c r="B188" t="s">
+        <v>925</v>
+      </c>
+      <c r="C188" t="s">
+        <v>926</v>
+      </c>
+      <c r="D188" t="s">
+        <v>927</v>
+      </c>
+      <c r="E188" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>929</v>
+      </c>
+      <c r="B189" t="s">
+        <v>930</v>
+      </c>
+      <c r="C189" t="s">
+        <v>931</v>
+      </c>
+      <c r="D189" t="s">
+        <v>932</v>
+      </c>
+      <c r="E189" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>934</v>
+      </c>
+      <c r="B190" t="s">
+        <v>935</v>
+      </c>
+      <c r="C190" t="s">
+        <v>936</v>
+      </c>
+      <c r="D190" t="s">
+        <v>937</v>
+      </c>
+      <c r="E190" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>939</v>
+      </c>
+      <c r="B191" t="s">
+        <v>940</v>
+      </c>
+      <c r="C191" t="s">
+        <v>941</v>
+      </c>
+      <c r="D191" t="s">
+        <v>942</v>
+      </c>
+      <c r="E191" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>944</v>
+      </c>
+      <c r="B192" t="s">
+        <v>945</v>
+      </c>
+      <c r="C192" t="s">
+        <v>946</v>
+      </c>
+      <c r="D192" t="s">
+        <v>947</v>
+      </c>
+      <c r="E192" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>949</v>
+      </c>
+      <c r="B193" t="s">
+        <v>950</v>
+      </c>
+      <c r="C193" t="s">
+        <v>951</v>
+      </c>
+      <c r="D193" t="s">
+        <v>952</v>
+      </c>
+      <c r="E193" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>954</v>
+      </c>
+      <c r="B194" t="s">
+        <v>955</v>
+      </c>
+      <c r="C194" t="s">
+        <v>956</v>
+      </c>
+      <c r="D194" t="s">
+        <v>957</v>
+      </c>
+      <c r="E194" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>959</v>
+      </c>
+      <c r="B195" t="s">
+        <v>959</v>
+      </c>
+      <c r="C195" t="s">
+        <v>960</v>
+      </c>
+      <c r="D195" t="s">
+        <v>707</v>
+      </c>
+      <c r="E195" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>961</v>
+      </c>
+      <c r="B196" t="s">
+        <v>961</v>
+      </c>
+      <c r="C196" t="s">
+        <v>962</v>
+      </c>
+      <c r="D196" t="s">
+        <v>702</v>
+      </c>
+      <c r="E196" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>963</v>
+      </c>
+      <c r="B197" t="s">
+        <v>964</v>
+      </c>
+      <c r="C197" t="s">
+        <v>965</v>
+      </c>
+      <c r="D197" t="s">
+        <v>966</v>
+      </c>
+      <c r="E197" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>968</v>
+      </c>
+      <c r="B198" t="s">
+        <v>552</v>
+      </c>
+      <c r="C198" t="s">
+        <v>969</v>
+      </c>
+      <c r="D198" t="s">
+        <v>970</v>
+      </c>
+      <c r="E198" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>972</v>
+      </c>
+      <c r="B199" t="s">
+        <v>973</v>
+      </c>
+      <c r="C199" t="s">
+        <v>974</v>
+      </c>
+      <c r="D199" t="s">
+        <v>975</v>
+      </c>
+      <c r="E199" t="s">
+        <v>976</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
